--- a/Etapa Construcción - Iteración 1/ESTIMACION DE CU.xlsx
+++ b/Etapa Construcción - Iteración 1/ESTIMACION DE CU.xlsx
@@ -12,12 +12,12 @@
     <definedName localSheetId="0" name="solver_typ">1</definedName>
     <definedName localSheetId="0" name="solver_val">0</definedName>
     <definedName localSheetId="0" name="solver_ver">3</definedName>
-    <definedName localSheetId="0" name="solver_opt">Plantilla!$D$62</definedName>
+    <definedName localSheetId="0" name="solver_opt">Plantilla!$D$60</definedName>
   </definedNames>
   <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="IzkSwoG8QFoHxXVdKUB5QN1RnAWF1Ud0Zx0Py/XcvR0="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="/vTAOJNM/L+IAKJmmRnBScpoovWEFxvI75uvJ9vv3eQ="/>
     </ext>
   </extLst>
 </workbook>
@@ -29,7 +29,7 @@
     <author/>
   </authors>
   <commentList>
-    <comment authorId="0" ref="B36">
+    <comment authorId="0" ref="B34">
       <text>
         <t xml:space="preserve">======
 ID#AAABrntIk4A
@@ -37,7 +37,7 @@
 ¿Hace falta consideraciones especiales para el acceso concurrente (paralelo) a datos y otros recursos?</t>
       </text>
     </comment>
-    <comment authorId="0" ref="B47">
+    <comment authorId="0" ref="B45">
       <text>
         <t xml:space="preserve">======
 ID#AAABrntIk4I
@@ -45,7 +45,7 @@
 Se refiere exclusivamente a la experiencia en el análisis, modelado, diseño y progrmación  mediante el paradigma de OO.</t>
       </text>
     </comment>
-    <comment authorId="0" ref="B48">
+    <comment authorId="0" ref="B46">
       <text>
         <t xml:space="preserve">======
 ID#AAABrntIk4E
@@ -53,20 +53,20 @@
 Se refiere a la experiencia en el análisis de requerimientos y modelado orientado a objetos del Analista Principal.</t>
       </text>
     </comment>
-    <comment authorId="0" ref="B51">
+    <comment authorId="0" ref="B69">
+      <text>
+        <t xml:space="preserve">======
+ID#AAABrntIk4Q
+Autor    (2023-08-29 20:18:46)
+Análisis/Diseño/Pruebas/Sobrecarga</t>
+      </text>
+    </comment>
+    <comment authorId="0" ref="B49">
       <text>
         <t xml:space="preserve">======
 ID#AAABrntIk30
 Autor    (2023-08-29 20:18:46)
 Este es un factor con signo opuesto a los factores E6 y anteriores. Cuanto mayor la evaluación, peor el resultado.</t>
-      </text>
-    </comment>
-    <comment authorId="0" ref="B71">
-      <text>
-        <t xml:space="preserve">======
-ID#AAABrntIk4Q
-Autor    (2023-08-29 20:18:46)
-Análisis/Diseño/Pruebas/Sobrecarga</t>
       </text>
     </comment>
     <comment authorId="0" ref="C14">
@@ -81,7 +81,7 @@
 -&gt; suma = 4 transacciones</t>
       </text>
     </comment>
-    <comment authorId="0" ref="B45">
+    <comment authorId="0" ref="B43">
       <text>
         <t xml:space="preserve">======
 ID#AAABrntIk3w
@@ -89,7 +89,15 @@
 Debe reflejar el hecho de que el equipo conoce el proceso y el lenguaje de modelado (p.ej.: RUP, UML). Puede ser cualquier otro proceso.</t>
       </text>
     </comment>
-    <comment authorId="0" ref="B74">
+    <comment authorId="0" ref="B47">
+      <text>
+        <t xml:space="preserve">======
+ID#AAABrntIk4Y
+Autor    (2023-08-29 20:18:46)
+Motivación del equipo.</t>
+      </text>
+    </comment>
+    <comment authorId="0" ref="B72">
       <text>
         <t xml:space="preserve">======
 ID#AAABrntIk38
@@ -97,15 +105,7 @@
 Lo debe sugerir el estimador.</t>
       </text>
     </comment>
-    <comment authorId="0" ref="B49">
-      <text>
-        <t xml:space="preserve">======
-ID#AAABrntIk4Y
-Autor    (2023-08-29 20:18:46)
-Motivación del equipo.</t>
-      </text>
-    </comment>
-    <comment authorId="0" ref="B32">
+    <comment authorId="0" ref="B30">
       <text>
         <t xml:space="preserve">======
 ID#AAABrntIk4U
@@ -113,7 +113,7 @@
 ¿La aplicación debe ser de fácil instalación (para usuarios sin capacidad técnica) o no?</t>
       </text>
     </comment>
-    <comment authorId="0" ref="B29">
+    <comment authorId="0" ref="B27">
       <text>
         <t xml:space="preserve">======
 ID#AAABrntIk34
@@ -121,7 +121,7 @@
 ¿La aplicacion está diseñada para que el usuario incremente SU eficiencia (no solo cumpla su cometido)?</t>
       </text>
     </comment>
-    <comment authorId="0" ref="B52">
+    <comment authorId="0" ref="B50">
       <text>
         <t xml:space="preserve">======
 ID#AAABrntIk5A
@@ -143,7 +143,7 @@
   - Otro sistema a través de una Interfaz de Programación de Aplicaciones (API)</t>
       </text>
     </comment>
-    <comment authorId="0" ref="B31">
+    <comment authorId="0" ref="B29">
       <text>
         <t xml:space="preserve">======
 ID#AAABrntIk4g
@@ -151,7 +151,7 @@
 ¿La aplicación requiere diseñarse para ser altamente reusable?</t>
       </text>
     </comment>
-    <comment authorId="0" ref="B34">
+    <comment authorId="0" ref="B32">
       <text>
         <t xml:space="preserve">======
 ID#AAABrntIk5E
@@ -159,7 +159,7 @@
 ¿La aplicación, debe funcionar en más de una plataforma?</t>
       </text>
     </comment>
-    <comment authorId="0" ref="B28">
+    <comment authorId="0" ref="B26">
       <text>
         <t xml:space="preserve">======
 ID#AAABrntIk4c
@@ -167,15 +167,7 @@
 ¿Cuál es la importancia del tiempo de respuesta de la aplicación para el usuario final?</t>
       </text>
     </comment>
-    <comment authorId="0" ref="B35">
-      <text>
-        <t xml:space="preserve">======
-ID#AAABrntIk40
-Autor    (2023-08-29 20:18:46)
-¿El cliente requiere que la aplicación se pueda cambiar fácilmente en el futuro?</t>
-      </text>
-    </comment>
-    <comment authorId="0" ref="B50">
+    <comment authorId="0" ref="B48">
       <text>
         <t xml:space="preserve">======
 ID#AAABrntIk5Q
@@ -186,12 +178,20 @@
     <comment authorId="0" ref="B33">
       <text>
         <t xml:space="preserve">======
+ID#AAABrntIk40
+Autor    (2023-08-29 20:18:46)
+¿El cliente requiere que la aplicación se pueda cambiar fácilmente en el futuro?</t>
+      </text>
+    </comment>
+    <comment authorId="0" ref="B31">
+      <text>
+        <t xml:space="preserve">======
 ID#AAABrntIk4o
 Autor    (2023-08-29 20:18:46)
 ¿Hay requerimientos especiales respecto de la facilidad de uso?</t>
       </text>
     </comment>
-    <comment authorId="0" ref="B27">
+    <comment authorId="0" ref="B25">
       <text>
         <t xml:space="preserve">======
 ID#AAABrntIk5M
@@ -199,7 +199,7 @@
 ¿Arquitectura centralizada o distribuida?</t>
       </text>
     </comment>
-    <comment authorId="0" ref="B39">
+    <comment authorId="0" ref="B37">
       <text>
         <t xml:space="preserve">======
 ID#AAABrntIk4k
@@ -207,7 +207,15 @@
 ¿Se requiere formación específica para los Usuarios?</t>
       </text>
     </comment>
-    <comment authorId="0" ref="B38">
+    <comment authorId="0" ref="B66">
+      <text>
+        <t xml:space="preserve">======
+ID#AAABrntIk5Y
+Autor    (2023-08-29 20:18:46)
+Esta distribución es una referencia. Proyecto a proyecto debe actualizarse mediante  ESTADISTICAS.</t>
+      </text>
+    </comment>
+    <comment authorId="0" ref="B36">
       <text>
         <t xml:space="preserve">======
 ID#AAABrntIk48
@@ -215,15 +223,7 @@
 ¿Nuestro código usará componentes COTS, librerías frameworks ya desarrollados? Si así fuera, reducirá la carga de trabajo de desarrollo.</t>
       </text>
     </comment>
-    <comment authorId="0" ref="B68">
-      <text>
-        <t xml:space="preserve">======
-ID#AAABrntIk5Y
-Autor    (2023-08-29 20:18:46)
-Esta distribución es una referencia. Proyecto a proyecto debe actualizarse mediante  ESTADISTICAS.</t>
-      </text>
-    </comment>
-    <comment authorId="0" ref="G62">
+    <comment authorId="0" ref="G60">
       <text>
         <t xml:space="preserve">======
 ID#AAABrntIk4w
@@ -234,7 +234,15 @@
 Es una Estadística que debe actualizarse proyecto a proyecto.</t>
       </text>
     </comment>
-    <comment authorId="0" ref="B37">
+    <comment authorId="0" ref="B44">
+      <text>
+        <t xml:space="preserve">======
+ID#AAABrntIk5U
+Autor    (2023-08-29 20:18:46)
+¿Ya trabajado el equipo en el area (dominio) de la aplicación?</t>
+      </text>
+    </comment>
+    <comment authorId="0" ref="B35">
       <text>
         <t xml:space="preserve">======
 ID#AAABrntIk44
@@ -242,15 +250,7 @@
 ¿Es suficiente con las prestaciones de seguridad normales, o hace falta algo especial?</t>
       </text>
     </comment>
-    <comment authorId="0" ref="B46">
-      <text>
-        <t xml:space="preserve">======
-ID#AAABrntIk5U
-Autor    (2023-08-29 20:18:46)
-¿Ya trabajado el equipo en el area (dominio) de la aplicación?</t>
-      </text>
-    </comment>
-    <comment authorId="0" ref="B30">
+    <comment authorId="0" ref="B28">
       <text>
         <t xml:space="preserve">======
 ID#AAABrntIk4s
@@ -261,14 +261,14 @@
   </commentList>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId1" roundtripDataSignature="AMtx7mghOhomtIhPakIKQ72avwPdiF9vxA=="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId1" roundtripDataSignature="AMtx7mjtL1bGlJRnrH0A8CfkYjIcb+rOHA=="/>
     </ext>
   </extLst>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="119">
   <si>
     <t>ESTIMACIÓN por PUNTOS de CASO de USO</t>
   </si>
@@ -343,12 +343,6 @@
   </si>
   <si>
     <t>Complejidad</t>
-  </si>
-  <si>
-    <t>CU23: Registrar usuario a proyecto</t>
-  </si>
-  <si>
-    <t>CU05: Crear Proyecto</t>
   </si>
   <si>
     <t>CU##: Gestionar tareas</t>
@@ -1177,7 +1171,7 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>590550</xdr:colOff>
-      <xdr:row>61</xdr:row>
+      <xdr:row>59</xdr:row>
       <xdr:rowOff>238125</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="4714875" cy="2667000"/>
@@ -2109,17 +2103,17 @@
       <c r="B16" s="21" t="s">
         <v>25</v>
       </c>
-      <c r="C16" s="21"/>
-      <c r="D16" s="34">
-        <v>6.0</v>
+      <c r="C16" s="36"/>
+      <c r="D16" s="37">
+        <v>10.0</v>
       </c>
       <c r="E16" s="24" t="str">
-        <f t="shared" ref="E16:E18" si="1">IF($D16&gt;0,IF($D16&lt;=3,"Simple",IF(AND($D16&gt;3,$D16&lt;7),"Intermedio",IF($D16&gt;=7,"Complejo","error"))),"-")</f>
-        <v>Intermedio</v>
+        <f>IF($D16&gt;0,IF($D16&lt;=3,"Simple",IF(AND($D16&gt;3,$D16&lt;7),"Intermedio",IF($D16&gt;=7,"Complejo","error"))),"-")</f>
+        <v>Complejo</v>
       </c>
       <c r="F16" s="24">
-        <f t="shared" ref="F16:F18" si="2">IF($D16&gt;0,IF($D16&lt;=3,5,IF(AND($D16&gt;3,$D16&lt;7),10,IF($D16&gt;=7,15,"error"))),0)</f>
-        <v>10</v>
+        <f>IF($D16&gt;0,IF($D16&lt;=3,5,IF(AND($D16&gt;3,$D16&lt;7),10,IF($D16&gt;=7,15,"error"))),0)</f>
+        <v>15</v>
       </c>
       <c r="G16" s="1"/>
       <c r="H16" s="1"/>
@@ -2147,17 +2141,15 @@
       <c r="B17" s="21" t="s">
         <v>26</v>
       </c>
-      <c r="C17" s="21"/>
-      <c r="D17" s="34">
-        <v>2.0</v>
-      </c>
-      <c r="E17" s="24" t="str">
-        <f t="shared" si="1"/>
-        <v>Simple</v>
+      <c r="C17" s="36"/>
+      <c r="D17" s="37">
+        <v>4.0</v>
+      </c>
+      <c r="E17" s="24" t="s">
+        <v>27</v>
       </c>
       <c r="F17" s="24">
-        <f t="shared" si="2"/>
-        <v>5</v>
+        <v>10.0</v>
       </c>
       <c r="G17" s="1"/>
       <c r="H17" s="1"/>
@@ -2182,20 +2174,15 @@
     </row>
     <row r="18" ht="27.75" customHeight="1">
       <c r="A18" s="1"/>
-      <c r="B18" s="21" t="s">
-        <v>27</v>
-      </c>
-      <c r="C18" s="36"/>
-      <c r="D18" s="37">
-        <v>10.0</v>
-      </c>
-      <c r="E18" s="24" t="str">
-        <f t="shared" si="1"/>
-        <v>Complejo</v>
-      </c>
-      <c r="F18" s="24">
-        <f t="shared" si="2"/>
-        <v>15</v>
+      <c r="B18" s="38"/>
+      <c r="C18" s="39" t="s">
+        <v>28</v>
+      </c>
+      <c r="D18" s="40"/>
+      <c r="E18" s="41"/>
+      <c r="F18" s="42">
+        <f>SUM(F15:F17)</f>
+        <v>25</v>
       </c>
       <c r="G18" s="1"/>
       <c r="H18" s="1"/>
@@ -2220,21 +2207,13 @@
     </row>
     <row r="19" ht="27.75" customHeight="1">
       <c r="A19" s="1"/>
-      <c r="B19" s="21" t="s">
-        <v>28</v>
-      </c>
-      <c r="C19" s="36"/>
-      <c r="D19" s="37">
-        <v>4.0</v>
-      </c>
-      <c r="E19" s="24" t="s">
-        <v>29</v>
-      </c>
-      <c r="F19" s="24">
-        <v>10.0</v>
-      </c>
+      <c r="B19" s="1"/>
+      <c r="C19" s="1"/>
+      <c r="D19" s="2"/>
+      <c r="E19" s="3"/>
+      <c r="F19" s="1"/>
       <c r="G19" s="1"/>
-      <c r="H19" s="1"/>
+      <c r="H19" s="18"/>
       <c r="I19" s="1"/>
       <c r="J19" s="1"/>
       <c r="K19" s="35"/>
@@ -2246,7 +2225,7 @@
       <c r="Q19" s="1"/>
       <c r="R19" s="1"/>
       <c r="S19" s="1"/>
-      <c r="T19" s="35"/>
+      <c r="T19" s="1"/>
       <c r="U19" s="1"/>
       <c r="V19" s="1"/>
       <c r="W19" s="1"/>
@@ -2256,21 +2235,16 @@
     </row>
     <row r="20" ht="27.75" customHeight="1">
       <c r="A20" s="1"/>
-      <c r="B20" s="38"/>
-      <c r="C20" s="39" t="s">
-        <v>30</v>
-      </c>
-      <c r="D20" s="40"/>
-      <c r="E20" s="41"/>
-      <c r="F20" s="42">
-        <f>SUM(F15:F19)</f>
-        <v>40</v>
-      </c>
+      <c r="B20" s="1"/>
+      <c r="C20" s="1"/>
+      <c r="D20" s="2"/>
+      <c r="E20" s="3"/>
+      <c r="F20" s="1"/>
       <c r="G20" s="1"/>
       <c r="H20" s="1"/>
       <c r="I20" s="1"/>
       <c r="J20" s="1"/>
-      <c r="K20" s="35"/>
+      <c r="K20" s="1"/>
       <c r="L20" s="1"/>
       <c r="M20" s="1"/>
       <c r="N20" s="1"/>
@@ -2279,7 +2253,7 @@
       <c r="Q20" s="1"/>
       <c r="R20" s="1"/>
       <c r="S20" s="1"/>
-      <c r="T20" s="35"/>
+      <c r="T20" s="1"/>
       <c r="U20" s="1"/>
       <c r="V20" s="1"/>
       <c r="W20" s="1"/>
@@ -2288,17 +2262,24 @@
       <c r="Z20" s="1"/>
     </row>
     <row r="21" ht="27.75" customHeight="1">
-      <c r="A21" s="1"/>
-      <c r="B21" s="1"/>
-      <c r="C21" s="1"/>
-      <c r="D21" s="2"/>
-      <c r="E21" s="3"/>
-      <c r="F21" s="1"/>
+      <c r="A21" s="18" t="s">
+        <v>29</v>
+      </c>
+      <c r="B21" s="43"/>
+      <c r="C21" s="28" t="s">
+        <v>30</v>
+      </c>
+      <c r="D21" s="6"/>
+      <c r="E21" s="7"/>
+      <c r="F21" s="29">
+        <f>G11+F18</f>
+        <v>28</v>
+      </c>
       <c r="G21" s="1"/>
-      <c r="H21" s="18"/>
+      <c r="H21" s="1"/>
       <c r="I21" s="1"/>
       <c r="J21" s="1"/>
-      <c r="K21" s="35"/>
+      <c r="K21" s="1"/>
       <c r="L21" s="1"/>
       <c r="M21" s="1"/>
       <c r="N21" s="1"/>
@@ -2323,7 +2304,7 @@
       <c r="E22" s="3"/>
       <c r="F22" s="1"/>
       <c r="G22" s="1"/>
-      <c r="H22" s="1"/>
+      <c r="H22" s="18"/>
       <c r="I22" s="1"/>
       <c r="J22" s="1"/>
       <c r="K22" s="1"/>
@@ -2344,19 +2325,12 @@
       <c r="Z22" s="1"/>
     </row>
     <row r="23" ht="27.75" customHeight="1">
-      <c r="A23" s="18" t="s">
-        <v>31</v>
-      </c>
-      <c r="B23" s="43"/>
-      <c r="C23" s="28" t="s">
-        <v>32</v>
-      </c>
-      <c r="D23" s="6"/>
-      <c r="E23" s="7"/>
-      <c r="F23" s="29">
-        <f>G11+F20</f>
-        <v>43</v>
-      </c>
+      <c r="A23" s="1"/>
+      <c r="B23" s="3"/>
+      <c r="C23" s="1"/>
+      <c r="D23" s="2"/>
+      <c r="E23" s="3"/>
+      <c r="F23" s="1"/>
       <c r="G23" s="1"/>
       <c r="H23" s="1"/>
       <c r="I23" s="1"/>
@@ -2379,14 +2353,28 @@
       <c r="Z23" s="1"/>
     </row>
     <row r="24" ht="27.75" customHeight="1">
-      <c r="A24" s="1"/>
-      <c r="B24" s="1"/>
-      <c r="C24" s="1"/>
-      <c r="D24" s="2"/>
-      <c r="E24" s="3"/>
-      <c r="F24" s="1"/>
-      <c r="G24" s="1"/>
-      <c r="H24" s="18"/>
+      <c r="A24" s="18" t="s">
+        <v>31</v>
+      </c>
+      <c r="B24" s="20" t="s">
+        <v>32</v>
+      </c>
+      <c r="C24" s="20" t="s">
+        <v>33</v>
+      </c>
+      <c r="D24" s="19" t="s">
+        <v>34</v>
+      </c>
+      <c r="E24" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="F24" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="G24" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="H24" s="1"/>
       <c r="I24" s="1"/>
       <c r="J24" s="1"/>
       <c r="K24" s="1"/>
@@ -2408,55 +2396,71 @@
     </row>
     <row r="25" ht="27.75" customHeight="1">
       <c r="A25" s="1"/>
-      <c r="B25" s="3"/>
-      <c r="C25" s="1"/>
-      <c r="D25" s="2"/>
-      <c r="E25" s="3"/>
-      <c r="F25" s="1"/>
-      <c r="G25" s="1"/>
-      <c r="H25" s="1"/>
-      <c r="I25" s="1"/>
-      <c r="J25" s="1"/>
-      <c r="K25" s="1"/>
-      <c r="L25" s="1"/>
-      <c r="M25" s="1"/>
-      <c r="N25" s="1"/>
-      <c r="O25" s="1"/>
-      <c r="P25" s="1"/>
-      <c r="Q25" s="1"/>
-      <c r="R25" s="1"/>
-      <c r="S25" s="1"/>
-      <c r="T25" s="1"/>
-      <c r="U25" s="1"/>
-      <c r="V25" s="1"/>
-      <c r="W25" s="1"/>
-      <c r="X25" s="1"/>
-      <c r="Y25" s="1"/>
-      <c r="Z25" s="1"/>
+      <c r="B25" s="44" t="s">
+        <v>37</v>
+      </c>
+      <c r="C25" s="44" t="s">
+        <v>38</v>
+      </c>
+      <c r="D25" s="45" t="s">
+        <v>39</v>
+      </c>
+      <c r="E25" s="46">
+        <v>2.0</v>
+      </c>
+      <c r="F25" s="25">
+        <v>0.0</v>
+      </c>
+      <c r="G25" s="47">
+        <f t="shared" ref="G25:G37" si="1">E25*F25</f>
+        <v>0</v>
+      </c>
+      <c r="H25" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="I25" s="18"/>
+      <c r="J25" s="18"/>
+      <c r="K25" s="18"/>
+      <c r="L25" s="18"/>
+      <c r="M25" s="18"/>
+      <c r="N25" s="18"/>
+      <c r="O25" s="18"/>
+      <c r="P25" s="18"/>
+      <c r="Q25" s="18"/>
+      <c r="R25" s="18"/>
+      <c r="S25" s="18"/>
+      <c r="T25" s="18"/>
+      <c r="U25" s="18"/>
+      <c r="V25" s="18"/>
+      <c r="W25" s="18"/>
+      <c r="X25" s="18"/>
+      <c r="Y25" s="18"/>
+      <c r="Z25" s="18"/>
     </row>
     <row r="26" ht="27.75" customHeight="1">
-      <c r="A26" s="18" t="s">
-        <v>33</v>
-      </c>
-      <c r="B26" s="20" t="s">
-        <v>34</v>
-      </c>
-      <c r="C26" s="20" t="s">
-        <v>35</v>
-      </c>
-      <c r="D26" s="19" t="s">
-        <v>36</v>
-      </c>
-      <c r="E26" s="19" t="s">
-        <v>9</v>
-      </c>
-      <c r="F26" s="19" t="s">
-        <v>37</v>
-      </c>
-      <c r="G26" s="19" t="s">
+      <c r="A26" s="1"/>
+      <c r="B26" s="44" t="s">
+        <v>41</v>
+      </c>
+      <c r="C26" s="44" t="s">
         <v>38</v>
       </c>
-      <c r="H26" s="1"/>
+      <c r="D26" s="48" t="s">
+        <v>42</v>
+      </c>
+      <c r="E26" s="47">
+        <v>2.0</v>
+      </c>
+      <c r="F26" s="25">
+        <v>5.0</v>
+      </c>
+      <c r="G26" s="47">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="H26" s="49" t="s">
+        <v>43</v>
+      </c>
       <c r="I26" s="1"/>
       <c r="J26" s="1"/>
       <c r="K26" s="1"/>
@@ -2476,73 +2480,67 @@
       <c r="Y26" s="1"/>
       <c r="Z26" s="1"/>
     </row>
-    <row r="27" ht="27.75" customHeight="1">
+    <row r="27" ht="27.0" customHeight="1">
       <c r="A27" s="1"/>
       <c r="B27" s="44" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="C27" s="44" t="s">
-        <v>40</v>
-      </c>
-      <c r="D27" s="45" t="s">
-        <v>41</v>
-      </c>
-      <c r="E27" s="46">
-        <v>2.0</v>
+        <v>38</v>
+      </c>
+      <c r="D27" s="48"/>
+      <c r="E27" s="47">
+        <v>1.0</v>
       </c>
       <c r="F27" s="25">
-        <v>0.0</v>
+        <v>5.0</v>
       </c>
       <c r="G27" s="47">
-        <f t="shared" ref="G27:G39" si="3">E27*F27</f>
-        <v>0</v>
-      </c>
-      <c r="H27" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="I27" s="18"/>
-      <c r="J27" s="18"/>
-      <c r="K27" s="18"/>
-      <c r="L27" s="18"/>
-      <c r="M27" s="18"/>
-      <c r="N27" s="18"/>
-      <c r="O27" s="18"/>
-      <c r="P27" s="18"/>
-      <c r="Q27" s="18"/>
-      <c r="R27" s="18"/>
-      <c r="S27" s="18"/>
-      <c r="T27" s="18"/>
-      <c r="U27" s="18"/>
-      <c r="V27" s="18"/>
-      <c r="W27" s="18"/>
-      <c r="X27" s="18"/>
-      <c r="Y27" s="18"/>
-      <c r="Z27" s="18"/>
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+      <c r="H27" s="1"/>
+      <c r="I27" s="1"/>
+      <c r="J27" s="1"/>
+      <c r="K27" s="1"/>
+      <c r="L27" s="1"/>
+      <c r="M27" s="1"/>
+      <c r="N27" s="1"/>
+      <c r="O27" s="1"/>
+      <c r="P27" s="1"/>
+      <c r="Q27" s="1"/>
+      <c r="R27" s="1"/>
+      <c r="S27" s="1"/>
+      <c r="T27" s="1"/>
+      <c r="U27" s="1"/>
+      <c r="V27" s="1"/>
+      <c r="W27" s="1"/>
+      <c r="X27" s="1"/>
+      <c r="Y27" s="1"/>
+      <c r="Z27" s="1"/>
     </row>
     <row r="28" ht="27.75" customHeight="1">
       <c r="A28" s="1"/>
       <c r="B28" s="44" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C28" s="44" t="s">
-        <v>40</v>
-      </c>
-      <c r="D28" s="48" t="s">
-        <v>44</v>
+        <v>38</v>
+      </c>
+      <c r="D28" s="45" t="s">
+        <v>46</v>
       </c>
       <c r="E28" s="47">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="F28" s="25">
-        <v>5.0</v>
+        <v>3.0</v>
       </c>
       <c r="G28" s="47">
-        <f t="shared" si="3"/>
-        <v>10</v>
-      </c>
-      <c r="H28" s="49" t="s">
-        <v>45</v>
-      </c>
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="H28" s="1"/>
       <c r="I28" s="1"/>
       <c r="J28" s="1"/>
       <c r="K28" s="1"/>
@@ -2562,24 +2560,26 @@
       <c r="Y28" s="1"/>
       <c r="Z28" s="1"/>
     </row>
-    <row r="29" ht="27.0" customHeight="1">
+    <row r="29" ht="30.75" customHeight="1">
       <c r="A29" s="1"/>
       <c r="B29" s="44" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C29" s="44" t="s">
-        <v>40</v>
-      </c>
-      <c r="D29" s="48"/>
-      <c r="E29" s="47">
+        <v>38</v>
+      </c>
+      <c r="D29" s="45" t="s">
+        <v>48</v>
+      </c>
+      <c r="E29" s="46">
         <v>1.0</v>
       </c>
       <c r="F29" s="25">
-        <v>5.0</v>
+        <v>0.0</v>
       </c>
       <c r="G29" s="47">
-        <f t="shared" si="3"/>
-        <v>5</v>
+        <f t="shared" si="1"/>
+        <v>0</v>
       </c>
       <c r="H29" s="1"/>
       <c r="I29" s="1"/>
@@ -2604,23 +2604,23 @@
     <row r="30" ht="27.75" customHeight="1">
       <c r="A30" s="1"/>
       <c r="B30" s="44" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C30" s="44" t="s">
-        <v>40</v>
-      </c>
-      <c r="D30" s="45" t="s">
-        <v>48</v>
-      </c>
-      <c r="E30" s="47">
-        <v>1.0</v>
+        <v>38</v>
+      </c>
+      <c r="D30" s="48" t="s">
+        <v>50</v>
+      </c>
+      <c r="E30" s="46">
+        <v>0.5</v>
       </c>
       <c r="F30" s="25">
         <v>3.0</v>
       </c>
       <c r="G30" s="47">
-        <f t="shared" si="3"/>
-        <v>3</v>
+        <f t="shared" si="1"/>
+        <v>1.5</v>
       </c>
       <c r="H30" s="1"/>
       <c r="I30" s="1"/>
@@ -2642,26 +2642,26 @@
       <c r="Y30" s="1"/>
       <c r="Z30" s="1"/>
     </row>
-    <row r="31" ht="30.75" customHeight="1">
+    <row r="31" ht="27.75" customHeight="1">
       <c r="A31" s="1"/>
       <c r="B31" s="44" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C31" s="44" t="s">
-        <v>40</v>
-      </c>
-      <c r="D31" s="45" t="s">
-        <v>50</v>
+        <v>38</v>
+      </c>
+      <c r="D31" s="48" t="s">
+        <v>52</v>
       </c>
       <c r="E31" s="46">
-        <v>1.0</v>
+        <v>0.5</v>
       </c>
       <c r="F31" s="25">
-        <v>0.0</v>
+        <v>5.0</v>
       </c>
       <c r="G31" s="47">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f t="shared" si="1"/>
+        <v>2.5</v>
       </c>
       <c r="H31" s="1"/>
       <c r="I31" s="1"/>
@@ -2686,23 +2686,23 @@
     <row r="32" ht="27.75" customHeight="1">
       <c r="A32" s="1"/>
       <c r="B32" s="44" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C32" s="44" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D32" s="48" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="E32" s="46">
-        <v>0.5</v>
+        <v>2.0</v>
       </c>
       <c r="F32" s="25">
         <v>3.0</v>
       </c>
       <c r="G32" s="47">
-        <f t="shared" si="3"/>
-        <v>1.5</v>
+        <f t="shared" si="1"/>
+        <v>6</v>
       </c>
       <c r="H32" s="1"/>
       <c r="I32" s="1"/>
@@ -2727,23 +2727,23 @@
     <row r="33" ht="27.75" customHeight="1">
       <c r="A33" s="1"/>
       <c r="B33" s="44" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C33" s="44" t="s">
-        <v>40</v>
-      </c>
-      <c r="D33" s="48" t="s">
-        <v>54</v>
+        <v>38</v>
+      </c>
+      <c r="D33" s="45" t="s">
+        <v>56</v>
       </c>
       <c r="E33" s="46">
-        <v>0.5</v>
+        <v>1.0</v>
       </c>
       <c r="F33" s="25">
-        <v>5.0</v>
+        <v>0.0</v>
       </c>
       <c r="G33" s="47">
-        <f t="shared" si="3"/>
-        <v>2.5</v>
+        <f t="shared" si="1"/>
+        <v>0</v>
       </c>
       <c r="H33" s="1"/>
       <c r="I33" s="1"/>
@@ -2768,23 +2768,21 @@
     <row r="34" ht="27.75" customHeight="1">
       <c r="A34" s="1"/>
       <c r="B34" s="44" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C34" s="44" t="s">
-        <v>40</v>
-      </c>
-      <c r="D34" s="48" t="s">
-        <v>56</v>
-      </c>
+        <v>38</v>
+      </c>
+      <c r="D34" s="45"/>
       <c r="E34" s="46">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="F34" s="25">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
       <c r="G34" s="47">
-        <f t="shared" si="3"/>
-        <v>6</v>
+        <f t="shared" si="1"/>
+        <v>5</v>
       </c>
       <c r="H34" s="1"/>
       <c r="I34" s="1"/>
@@ -2809,23 +2807,23 @@
     <row r="35" ht="27.75" customHeight="1">
       <c r="A35" s="1"/>
       <c r="B35" s="44" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C35" s="44" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D35" s="45" t="s">
-        <v>58</v>
-      </c>
-      <c r="E35" s="46">
+        <v>59</v>
+      </c>
+      <c r="E35" s="47">
         <v>1.0</v>
       </c>
       <c r="F35" s="25">
-        <v>0.0</v>
+        <v>5.0</v>
       </c>
       <c r="G35" s="47">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f t="shared" si="1"/>
+        <v>5</v>
       </c>
       <c r="H35" s="1"/>
       <c r="I35" s="1"/>
@@ -2847,23 +2845,25 @@
       <c r="Y35" s="1"/>
       <c r="Z35" s="1"/>
     </row>
-    <row r="36" ht="27.75" customHeight="1">
+    <row r="36" ht="30.75" customHeight="1">
       <c r="A36" s="1"/>
       <c r="B36" s="44" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C36" s="44" t="s">
-        <v>40</v>
-      </c>
-      <c r="D36" s="45"/>
-      <c r="E36" s="46">
+        <v>38</v>
+      </c>
+      <c r="D36" s="45" t="s">
+        <v>61</v>
+      </c>
+      <c r="E36" s="47">
         <v>1.0</v>
       </c>
       <c r="F36" s="25">
         <v>5.0</v>
       </c>
       <c r="G36" s="47">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>5</v>
       </c>
       <c r="H36" s="1"/>
@@ -2886,26 +2886,26 @@
       <c r="Y36" s="1"/>
       <c r="Z36" s="1"/>
     </row>
-    <row r="37" ht="27.75" customHeight="1">
+    <row r="37" ht="31.5" customHeight="1">
       <c r="A37" s="1"/>
       <c r="B37" s="44" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C37" s="44" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D37" s="45" t="s">
-        <v>61</v>
-      </c>
-      <c r="E37" s="47">
+        <v>63</v>
+      </c>
+      <c r="E37" s="46">
         <v>1.0</v>
       </c>
       <c r="F37" s="25">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
       <c r="G37" s="47">
-        <f t="shared" si="3"/>
-        <v>5</v>
+        <f t="shared" si="1"/>
+        <v>4</v>
       </c>
       <c r="H37" s="1"/>
       <c r="I37" s="1"/>
@@ -2929,24 +2929,16 @@
     </row>
     <row r="38" ht="30.75" customHeight="1">
       <c r="A38" s="1"/>
-      <c r="B38" s="44" t="s">
-        <v>62</v>
-      </c>
-      <c r="C38" s="44" t="s">
-        <v>40</v>
-      </c>
-      <c r="D38" s="45" t="s">
-        <v>63</v>
-      </c>
-      <c r="E38" s="47">
-        <v>1.0</v>
-      </c>
-      <c r="F38" s="25">
-        <v>5.0</v>
-      </c>
-      <c r="G38" s="47">
-        <f t="shared" si="3"/>
-        <v>5</v>
+      <c r="B38" s="28" t="s">
+        <v>64</v>
+      </c>
+      <c r="C38" s="6"/>
+      <c r="D38" s="6"/>
+      <c r="E38" s="6"/>
+      <c r="F38" s="7"/>
+      <c r="G38" s="50">
+        <f>SUM(G25:G37)</f>
+        <v>47</v>
       </c>
       <c r="H38" s="1"/>
       <c r="I38" s="1"/>
@@ -2968,26 +2960,18 @@
       <c r="Y38" s="1"/>
       <c r="Z38" s="1"/>
     </row>
-    <row r="39" ht="31.5" customHeight="1">
+    <row r="39" ht="27.75" customHeight="1">
       <c r="A39" s="1"/>
-      <c r="B39" s="44" t="s">
-        <v>64</v>
-      </c>
-      <c r="C39" s="44" t="s">
-        <v>40</v>
-      </c>
-      <c r="D39" s="45" t="s">
+      <c r="B39" s="28" t="s">
         <v>65</v>
       </c>
-      <c r="E39" s="46">
-        <v>1.0</v>
-      </c>
-      <c r="F39" s="25">
-        <v>4.0</v>
-      </c>
-      <c r="G39" s="47">
-        <f t="shared" si="3"/>
-        <v>4</v>
+      <c r="C39" s="6"/>
+      <c r="D39" s="6"/>
+      <c r="E39" s="6"/>
+      <c r="F39" s="7"/>
+      <c r="G39" s="42">
+        <f>0.6+(0.01*G38)</f>
+        <v>1.07</v>
       </c>
       <c r="H39" s="1"/>
       <c r="I39" s="1"/>
@@ -3009,19 +2993,14 @@
       <c r="Y39" s="1"/>
       <c r="Z39" s="1"/>
     </row>
-    <row r="40" ht="30.75" customHeight="1">
+    <row r="40" ht="27.75" customHeight="1">
       <c r="A40" s="1"/>
-      <c r="B40" s="28" t="s">
-        <v>66</v>
-      </c>
-      <c r="C40" s="6"/>
-      <c r="D40" s="6"/>
-      <c r="E40" s="6"/>
-      <c r="F40" s="7"/>
-      <c r="G40" s="50">
-        <f>SUM(G27:G39)</f>
-        <v>47</v>
-      </c>
+      <c r="B40" s="30"/>
+      <c r="C40" s="3"/>
+      <c r="D40" s="3"/>
+      <c r="E40" s="3"/>
+      <c r="F40" s="3"/>
+      <c r="G40" s="1"/>
       <c r="H40" s="1"/>
       <c r="I40" s="1"/>
       <c r="J40" s="1"/>
@@ -3044,17 +3023,12 @@
     </row>
     <row r="41" ht="27.75" customHeight="1">
       <c r="A41" s="1"/>
-      <c r="B41" s="28" t="s">
-        <v>67</v>
-      </c>
-      <c r="C41" s="6"/>
-      <c r="D41" s="6"/>
-      <c r="E41" s="6"/>
-      <c r="F41" s="7"/>
-      <c r="G41" s="42">
-        <f>0.6+(0.01*G40)</f>
-        <v>1.07</v>
-      </c>
+      <c r="B41" s="51"/>
+      <c r="C41" s="51"/>
+      <c r="D41" s="52"/>
+      <c r="E41" s="51"/>
+      <c r="F41" s="51"/>
+      <c r="G41" s="51"/>
       <c r="H41" s="1"/>
       <c r="I41" s="1"/>
       <c r="J41" s="1"/>
@@ -3076,13 +3050,27 @@
       <c r="Z41" s="1"/>
     </row>
     <row r="42" ht="27.75" customHeight="1">
-      <c r="A42" s="1"/>
-      <c r="B42" s="30"/>
-      <c r="C42" s="3"/>
-      <c r="D42" s="3"/>
-      <c r="E42" s="3"/>
-      <c r="F42" s="3"/>
-      <c r="G42" s="1"/>
+      <c r="A42" s="18" t="s">
+        <v>66</v>
+      </c>
+      <c r="B42" s="20" t="s">
+        <v>67</v>
+      </c>
+      <c r="C42" s="20" t="s">
+        <v>68</v>
+      </c>
+      <c r="D42" s="19" t="s">
+        <v>69</v>
+      </c>
+      <c r="E42" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="F42" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="G42" s="19" t="s">
+        <v>36</v>
+      </c>
       <c r="H42" s="1"/>
       <c r="I42" s="1"/>
       <c r="J42" s="1"/>
@@ -3103,57 +3091,73 @@
       <c r="Y42" s="1"/>
       <c r="Z42" s="1"/>
     </row>
-    <row r="43" ht="27.75" customHeight="1">
+    <row r="43" ht="64.5" customHeight="1">
       <c r="A43" s="1"/>
-      <c r="B43" s="51"/>
-      <c r="C43" s="51"/>
-      <c r="D43" s="52"/>
-      <c r="E43" s="51"/>
-      <c r="F43" s="51"/>
-      <c r="G43" s="51"/>
-      <c r="H43" s="1"/>
-      <c r="I43" s="1"/>
-      <c r="J43" s="1"/>
-      <c r="K43" s="1"/>
-      <c r="L43" s="1"/>
-      <c r="M43" s="1"/>
-      <c r="N43" s="1"/>
-      <c r="O43" s="1"/>
-      <c r="P43" s="1"/>
-      <c r="Q43" s="1"/>
-      <c r="R43" s="1"/>
-      <c r="S43" s="1"/>
-      <c r="T43" s="1"/>
-      <c r="U43" s="1"/>
-      <c r="V43" s="1"/>
-      <c r="W43" s="1"/>
-      <c r="X43" s="1"/>
-      <c r="Y43" s="1"/>
-      <c r="Z43" s="1"/>
-    </row>
-    <row r="44" ht="27.75" customHeight="1">
-      <c r="A44" s="18" t="s">
-        <v>68</v>
-      </c>
-      <c r="B44" s="20" t="s">
-        <v>69</v>
-      </c>
-      <c r="C44" s="20" t="s">
+      <c r="B43" s="53" t="s">
         <v>70</v>
       </c>
-      <c r="D44" s="19" t="s">
+      <c r="C43" s="44" t="s">
         <v>71</v>
       </c>
-      <c r="E44" s="19" t="s">
-        <v>9</v>
-      </c>
-      <c r="F44" s="19" t="s">
-        <v>37</v>
-      </c>
-      <c r="G44" s="19" t="s">
-        <v>38</v>
-      </c>
-      <c r="H44" s="1"/>
+      <c r="D43" s="48" t="s">
+        <v>72</v>
+      </c>
+      <c r="E43" s="46">
+        <v>1.5</v>
+      </c>
+      <c r="F43" s="25">
+        <v>3.0</v>
+      </c>
+      <c r="G43" s="47">
+        <f t="shared" ref="G43:G50" si="2">E43*F43</f>
+        <v>4.5</v>
+      </c>
+      <c r="H43" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="I43" s="18"/>
+      <c r="J43" s="18"/>
+      <c r="K43" s="18"/>
+      <c r="L43" s="18"/>
+      <c r="M43" s="18"/>
+      <c r="N43" s="18"/>
+      <c r="O43" s="18"/>
+      <c r="P43" s="18"/>
+      <c r="Q43" s="18"/>
+      <c r="R43" s="18"/>
+      <c r="S43" s="18"/>
+      <c r="T43" s="18"/>
+      <c r="U43" s="18"/>
+      <c r="V43" s="18"/>
+      <c r="W43" s="18"/>
+      <c r="X43" s="18"/>
+      <c r="Y43" s="18"/>
+      <c r="Z43" s="18"/>
+    </row>
+    <row r="44" ht="51.0" customHeight="1">
+      <c r="A44" s="1"/>
+      <c r="B44" s="53" t="s">
+        <v>74</v>
+      </c>
+      <c r="C44" s="44" t="s">
+        <v>71</v>
+      </c>
+      <c r="D44" s="48" t="s">
+        <v>75</v>
+      </c>
+      <c r="E44" s="46">
+        <v>0.5</v>
+      </c>
+      <c r="F44" s="25">
+        <v>4.0</v>
+      </c>
+      <c r="G44" s="47">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+      <c r="H44" s="49" t="s">
+        <v>43</v>
+      </c>
       <c r="I44" s="1"/>
       <c r="J44" s="1"/>
       <c r="K44" s="1"/>
@@ -3173,73 +3177,69 @@
       <c r="Y44" s="1"/>
       <c r="Z44" s="1"/>
     </row>
-    <row r="45" ht="64.5" customHeight="1">
+    <row r="45" ht="48.75" customHeight="1">
       <c r="A45" s="1"/>
       <c r="B45" s="53" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="C45" s="44" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D45" s="48" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="E45" s="46">
-        <v>1.5</v>
+        <v>1.0</v>
       </c>
       <c r="F45" s="25">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="G45" s="47">
-        <f t="shared" ref="G45:G52" si="4">E45*F45</f>
-        <v>4.5</v>
-      </c>
-      <c r="H45" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="I45" s="18"/>
-      <c r="J45" s="18"/>
-      <c r="K45" s="18"/>
-      <c r="L45" s="18"/>
-      <c r="M45" s="18"/>
-      <c r="N45" s="18"/>
-      <c r="O45" s="18"/>
-      <c r="P45" s="18"/>
-      <c r="Q45" s="18"/>
-      <c r="R45" s="18"/>
-      <c r="S45" s="18"/>
-      <c r="T45" s="18"/>
-      <c r="U45" s="18"/>
-      <c r="V45" s="18"/>
-      <c r="W45" s="18"/>
-      <c r="X45" s="18"/>
-      <c r="Y45" s="18"/>
-      <c r="Z45" s="18"/>
-    </row>
-    <row r="46" ht="51.0" customHeight="1">
+        <f t="shared" si="2"/>
+        <v>4</v>
+      </c>
+      <c r="H45" s="1"/>
+      <c r="I45" s="1"/>
+      <c r="J45" s="1"/>
+      <c r="K45" s="1"/>
+      <c r="L45" s="1"/>
+      <c r="M45" s="1"/>
+      <c r="N45" s="1"/>
+      <c r="O45" s="1"/>
+      <c r="P45" s="1"/>
+      <c r="Q45" s="1"/>
+      <c r="R45" s="1"/>
+      <c r="S45" s="1"/>
+      <c r="T45" s="1"/>
+      <c r="U45" s="1"/>
+      <c r="V45" s="1"/>
+      <c r="W45" s="1"/>
+      <c r="X45" s="1"/>
+      <c r="Y45" s="1"/>
+      <c r="Z45" s="1"/>
+    </row>
+    <row r="46" ht="46.5" customHeight="1">
       <c r="A46" s="1"/>
       <c r="B46" s="53" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C46" s="44" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D46" s="48" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="E46" s="46">
         <v>0.5</v>
       </c>
       <c r="F46" s="25">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
       <c r="G46" s="47">
-        <f t="shared" si="4"/>
-        <v>2</v>
-      </c>
-      <c r="H46" s="49" t="s">
-        <v>45</v>
-      </c>
+        <f t="shared" si="2"/>
+        <v>1.5</v>
+      </c>
+      <c r="H46" s="1"/>
       <c r="I46" s="1"/>
       <c r="J46" s="1"/>
       <c r="K46" s="1"/>
@@ -3259,16 +3259,16 @@
       <c r="Y46" s="1"/>
       <c r="Z46" s="1"/>
     </row>
-    <row r="47" ht="48.75" customHeight="1">
+    <row r="47" ht="37.5" customHeight="1">
       <c r="A47" s="1"/>
       <c r="B47" s="53" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C47" s="44" t="s">
-        <v>73</v>
-      </c>
-      <c r="D47" s="48" t="s">
-        <v>79</v>
+        <v>81</v>
+      </c>
+      <c r="D47" s="45" t="s">
+        <v>82</v>
       </c>
       <c r="E47" s="46">
         <v>1.0</v>
@@ -3277,7 +3277,7 @@
         <v>4.0</v>
       </c>
       <c r="G47" s="47">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>4</v>
       </c>
       <c r="H47" s="1"/>
@@ -3300,26 +3300,26 @@
       <c r="Y47" s="1"/>
       <c r="Z47" s="1"/>
     </row>
-    <row r="48" ht="46.5" customHeight="1">
+    <row r="48" ht="43.5" customHeight="1">
       <c r="A48" s="1"/>
       <c r="B48" s="53" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="C48" s="44" t="s">
-        <v>73</v>
-      </c>
-      <c r="D48" s="48" t="s">
-        <v>81</v>
+        <v>84</v>
+      </c>
+      <c r="D48" s="45" t="s">
+        <v>85</v>
       </c>
       <c r="E48" s="46">
-        <v>0.5</v>
+        <v>2.0</v>
       </c>
       <c r="F48" s="25">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="G48" s="47">
-        <f t="shared" si="4"/>
-        <v>1.5</v>
+        <f t="shared" si="2"/>
+        <v>4</v>
       </c>
       <c r="H48" s="1"/>
       <c r="I48" s="1"/>
@@ -3341,26 +3341,26 @@
       <c r="Y48" s="1"/>
       <c r="Z48" s="1"/>
     </row>
-    <row r="49" ht="37.5" customHeight="1">
+    <row r="49" ht="71.25" customHeight="1">
       <c r="A49" s="1"/>
       <c r="B49" s="53" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="C49" s="44" t="s">
-        <v>83</v>
-      </c>
-      <c r="D49" s="45" t="s">
-        <v>84</v>
+        <v>87</v>
+      </c>
+      <c r="D49" s="48" t="s">
+        <v>88</v>
       </c>
       <c r="E49" s="46">
-        <v>1.0</v>
+        <v>-1.0</v>
       </c>
       <c r="F49" s="25">
         <v>4.0</v>
       </c>
       <c r="G49" s="47">
-        <f t="shared" si="4"/>
-        <v>4</v>
+        <f t="shared" si="2"/>
+        <v>-4</v>
       </c>
       <c r="H49" s="1"/>
       <c r="I49" s="1"/>
@@ -3382,26 +3382,26 @@
       <c r="Y49" s="1"/>
       <c r="Z49" s="1"/>
     </row>
-    <row r="50" ht="43.5" customHeight="1">
+    <row r="50" ht="62.25" customHeight="1">
       <c r="A50" s="1"/>
       <c r="B50" s="53" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="C50" s="44" t="s">
-        <v>86</v>
-      </c>
-      <c r="D50" s="45" t="s">
-        <v>87</v>
+        <v>90</v>
+      </c>
+      <c r="D50" s="48" t="s">
+        <v>91</v>
       </c>
       <c r="E50" s="46">
-        <v>2.0</v>
+        <v>-1.0</v>
       </c>
       <c r="F50" s="25">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
       <c r="G50" s="47">
-        <f t="shared" si="4"/>
-        <v>4</v>
+        <f t="shared" si="2"/>
+        <v>-4</v>
       </c>
       <c r="H50" s="1"/>
       <c r="I50" s="1"/>
@@ -3423,26 +3423,18 @@
       <c r="Y50" s="1"/>
       <c r="Z50" s="1"/>
     </row>
-    <row r="51" ht="71.25" customHeight="1">
+    <row r="51" ht="38.25" customHeight="1">
       <c r="A51" s="1"/>
-      <c r="B51" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="C51" s="44" t="s">
-        <v>89</v>
-      </c>
-      <c r="D51" s="48" t="s">
-        <v>90</v>
-      </c>
-      <c r="E51" s="46">
-        <v>-1.0</v>
-      </c>
-      <c r="F51" s="25">
-        <v>4.0</v>
-      </c>
-      <c r="G51" s="47">
-        <f t="shared" si="4"/>
-        <v>-4</v>
+      <c r="B51" s="28" t="s">
+        <v>92</v>
+      </c>
+      <c r="C51" s="6"/>
+      <c r="D51" s="6"/>
+      <c r="E51" s="6"/>
+      <c r="F51" s="7"/>
+      <c r="G51" s="19">
+        <f>SUM(G43:G50)</f>
+        <v>12</v>
       </c>
       <c r="H51" s="1"/>
       <c r="I51" s="1"/>
@@ -3464,26 +3456,18 @@
       <c r="Y51" s="1"/>
       <c r="Z51" s="1"/>
     </row>
-    <row r="52" ht="62.25" customHeight="1">
+    <row r="52" ht="27.75" customHeight="1">
       <c r="A52" s="1"/>
-      <c r="B52" s="53" t="s">
-        <v>91</v>
-      </c>
-      <c r="C52" s="44" t="s">
-        <v>92</v>
-      </c>
-      <c r="D52" s="48" t="s">
+      <c r="B52" s="28" t="s">
         <v>93</v>
       </c>
-      <c r="E52" s="46">
-        <v>-1.0</v>
-      </c>
-      <c r="F52" s="25">
-        <v>4.0</v>
-      </c>
-      <c r="G52" s="47">
-        <f t="shared" si="4"/>
-        <v>-4</v>
+      <c r="C52" s="6"/>
+      <c r="D52" s="6"/>
+      <c r="E52" s="6"/>
+      <c r="F52" s="7"/>
+      <c r="G52" s="19">
+        <f>1.4 + (-0.03*G51)</f>
+        <v>1.04</v>
       </c>
       <c r="H52" s="1"/>
       <c r="I52" s="1"/>
@@ -3505,18 +3489,18 @@
       <c r="Y52" s="1"/>
       <c r="Z52" s="1"/>
     </row>
-    <row r="53" ht="38.25" customHeight="1">
+    <row r="53" ht="27.75" customHeight="1">
       <c r="A53" s="1"/>
-      <c r="B53" s="28" t="s">
+      <c r="B53" s="28"/>
+      <c r="C53" s="54"/>
+      <c r="D53" s="55"/>
+      <c r="E53" s="54"/>
+      <c r="F53" s="56" t="s">
         <v>94</v>
       </c>
-      <c r="C53" s="6"/>
-      <c r="D53" s="6"/>
-      <c r="E53" s="6"/>
-      <c r="F53" s="7"/>
       <c r="G53" s="19">
-        <f>SUM(G45:G52)</f>
-        <v>12</v>
+        <f>COUNTIF($F$43:$F$48,"&lt;3")+COUNTIF($F$49:$F$50,"&gt;3")</f>
+        <v>3</v>
       </c>
       <c r="H53" s="1"/>
       <c r="I53" s="1"/>
@@ -3540,17 +3524,12 @@
     </row>
     <row r="54" ht="27.75" customHeight="1">
       <c r="A54" s="1"/>
-      <c r="B54" s="28" t="s">
-        <v>95</v>
-      </c>
-      <c r="C54" s="6"/>
-      <c r="D54" s="6"/>
-      <c r="E54" s="6"/>
-      <c r="F54" s="7"/>
-      <c r="G54" s="19">
-        <f>1.4 + (-0.03*G53)</f>
-        <v>1.04</v>
-      </c>
+      <c r="B54" s="30"/>
+      <c r="C54" s="3"/>
+      <c r="D54" s="3"/>
+      <c r="E54" s="3"/>
+      <c r="F54" s="3"/>
+      <c r="G54" s="1"/>
       <c r="H54" s="1"/>
       <c r="I54" s="1"/>
       <c r="J54" s="1"/>
@@ -3573,17 +3552,12 @@
     </row>
     <row r="55" ht="27.75" customHeight="1">
       <c r="A55" s="1"/>
-      <c r="B55" s="28"/>
-      <c r="C55" s="54"/>
-      <c r="D55" s="55"/>
-      <c r="E55" s="54"/>
-      <c r="F55" s="56" t="s">
-        <v>96</v>
-      </c>
-      <c r="G55" s="19">
-        <f>COUNTIF($F$45:$F$50,"&lt;3")+COUNTIF($F$51:$F$52,"&gt;3")</f>
-        <v>3</v>
-      </c>
+      <c r="B55" s="1"/>
+      <c r="C55" s="1"/>
+      <c r="D55" s="2"/>
+      <c r="E55" s="3"/>
+      <c r="F55" s="1"/>
+      <c r="G55" s="1"/>
       <c r="H55" s="1"/>
       <c r="I55" s="1"/>
       <c r="J55" s="1"/>
@@ -3605,13 +3579,20 @@
       <c r="Z55" s="1"/>
     </row>
     <row r="56" ht="27.75" customHeight="1">
-      <c r="A56" s="1"/>
-      <c r="B56" s="30"/>
-      <c r="C56" s="3"/>
-      <c r="D56" s="3"/>
-      <c r="E56" s="3"/>
-      <c r="F56" s="3"/>
-      <c r="G56" s="1"/>
+      <c r="A56" s="18" t="s">
+        <v>95</v>
+      </c>
+      <c r="B56" s="57" t="s">
+        <v>96</v>
+      </c>
+      <c r="C56" s="6"/>
+      <c r="D56" s="6"/>
+      <c r="E56" s="6"/>
+      <c r="F56" s="7"/>
+      <c r="G56" s="58">
+        <f>F21*G39*G52</f>
+        <v>31.1584</v>
+      </c>
       <c r="H56" s="1"/>
       <c r="I56" s="1"/>
       <c r="J56" s="1"/>
@@ -3661,20 +3642,13 @@
       <c r="Z57" s="1"/>
     </row>
     <row r="58" ht="27.75" customHeight="1">
-      <c r="A58" s="18" t="s">
-        <v>97</v>
-      </c>
-      <c r="B58" s="57" t="s">
-        <v>98</v>
-      </c>
-      <c r="C58" s="6"/>
-      <c r="D58" s="6"/>
-      <c r="E58" s="6"/>
-      <c r="F58" s="7"/>
-      <c r="G58" s="58">
-        <f>F23*G41*G54</f>
-        <v>47.8504</v>
-      </c>
+      <c r="A58" s="1"/>
+      <c r="B58" s="1"/>
+      <c r="C58" s="1"/>
+      <c r="D58" s="2"/>
+      <c r="E58" s="3"/>
+      <c r="F58" s="1"/>
+      <c r="G58" s="1"/>
       <c r="H58" s="1"/>
       <c r="I58" s="1"/>
       <c r="J58" s="1"/>
@@ -3696,13 +3670,23 @@
       <c r="Z58" s="1"/>
     </row>
     <row r="59" ht="27.75" customHeight="1">
-      <c r="A59" s="1"/>
-      <c r="B59" s="1"/>
-      <c r="C59" s="1"/>
-      <c r="D59" s="2"/>
+      <c r="A59" s="59" t="s">
+        <v>97</v>
+      </c>
+      <c r="B59" s="20" t="s">
+        <v>98</v>
+      </c>
+      <c r="C59" s="20" t="s">
+        <v>99</v>
+      </c>
+      <c r="D59" s="20" t="s">
+        <v>100</v>
+      </c>
       <c r="E59" s="3"/>
       <c r="F59" s="1"/>
-      <c r="G59" s="1"/>
+      <c r="G59" s="20" t="s">
+        <v>101</v>
+      </c>
       <c r="H59" s="1"/>
       <c r="I59" s="1"/>
       <c r="J59" s="1"/>
@@ -3723,14 +3707,24 @@
       <c r="Y59" s="1"/>
       <c r="Z59" s="1"/>
     </row>
-    <row r="60" ht="27.75" customHeight="1">
+    <row r="60" ht="31.5" customHeight="1">
       <c r="A60" s="1"/>
-      <c r="B60" s="1"/>
-      <c r="C60" s="1"/>
-      <c r="D60" s="2"/>
+      <c r="B60" s="60">
+        <v>20.0</v>
+      </c>
+      <c r="C60" s="60">
+        <f>IF($G$53&gt;=5,36,IF(AND(G$53&gt;2,$G$53&lt;=4),28, IF(AND($G$53&gt;=0,$G$53&lt;=2),20,"error")))</f>
+        <v>28</v>
+      </c>
+      <c r="D60" s="61">
+        <f>IF($G$53&gt;=5,$G$60*(36/20),IF(AND($G$53&gt;2,$G$53&lt;=4),$G$60*(28/20), IF(AND($G$53&gt;=0,$G$53&lt;=2),$G$60,"error")))</f>
+        <v>2.8</v>
+      </c>
       <c r="E60" s="3"/>
       <c r="F60" s="1"/>
-      <c r="G60" s="1"/>
+      <c r="G60" s="62">
+        <v>2.0</v>
+      </c>
       <c r="H60" s="1"/>
       <c r="I60" s="1"/>
       <c r="J60" s="1"/>
@@ -3752,23 +3746,15 @@
       <c r="Z60" s="1"/>
     </row>
     <row r="61" ht="27.75" customHeight="1">
-      <c r="A61" s="59" t="s">
-        <v>99</v>
-      </c>
-      <c r="B61" s="20" t="s">
-        <v>100</v>
-      </c>
-      <c r="C61" s="20" t="s">
-        <v>101</v>
-      </c>
-      <c r="D61" s="20" t="s">
+      <c r="A61" s="1"/>
+      <c r="B61" s="63" t="s">
         <v>102</v>
       </c>
+      <c r="C61" s="6"/>
+      <c r="D61" s="7"/>
       <c r="E61" s="3"/>
       <c r="F61" s="1"/>
-      <c r="G61" s="20" t="s">
-        <v>103</v>
-      </c>
+      <c r="G61" s="1"/>
       <c r="H61" s="1"/>
       <c r="I61" s="1"/>
       <c r="J61" s="1"/>
@@ -3789,24 +3775,25 @@
       <c r="Y61" s="1"/>
       <c r="Z61" s="1"/>
     </row>
-    <row r="62" ht="31.5" customHeight="1">
-      <c r="A62" s="1"/>
+    <row r="62" ht="27.75" customHeight="1">
+      <c r="A62" s="64" t="s">
+        <v>103</v>
+      </c>
       <c r="B62" s="60">
-        <v>20.0</v>
+        <f t="shared" ref="B62:D62" si="3">$G$56*B60</f>
+        <v>623.168</v>
       </c>
       <c r="C62" s="60">
-        <f>IF($G$55&gt;=5,36,IF(AND(G$55&gt;2,$G$55&lt;=4),28, IF(AND($G$55&gt;=0,$G$55&lt;=2),20,"error")))</f>
-        <v>28</v>
-      </c>
-      <c r="D62" s="61">
-        <f>IF($G$55&gt;=5,$G$62*(36/20),IF(AND($G$55&gt;2,$G$55&lt;=4),$G$62*(28/20), IF(AND($G$55&gt;=0,$G$55&lt;=2),$G$62,"error")))</f>
-        <v>2.8</v>
+        <f t="shared" si="3"/>
+        <v>872.4352</v>
+      </c>
+      <c r="D62" s="60">
+        <f t="shared" si="3"/>
+        <v>87.24352</v>
       </c>
       <c r="E62" s="3"/>
       <c r="F62" s="1"/>
-      <c r="G62" s="62">
-        <v>2.0</v>
-      </c>
+      <c r="G62" s="1"/>
       <c r="H62" s="1"/>
       <c r="I62" s="1"/>
       <c r="J62" s="1"/>
@@ -3828,12 +3815,21 @@
       <c r="Z62" s="1"/>
     </row>
     <row r="63" ht="27.75" customHeight="1">
-      <c r="A63" s="1"/>
-      <c r="B63" s="63" t="s">
+      <c r="A63" s="64" t="s">
         <v>104</v>
       </c>
-      <c r="C63" s="6"/>
-      <c r="D63" s="7"/>
+      <c r="B63" s="65">
+        <f t="shared" ref="B63:C63" si="4">B62/(22*8)</f>
+        <v>3.540727273</v>
+      </c>
+      <c r="C63" s="65">
+        <f t="shared" si="4"/>
+        <v>4.957018182</v>
+      </c>
+      <c r="D63" s="66">
+        <f>D62/(22*3)</f>
+        <v>1.321871515</v>
+      </c>
       <c r="E63" s="3"/>
       <c r="F63" s="1"/>
       <c r="G63" s="1"/>
@@ -3858,21 +3854,10 @@
       <c r="Z63" s="1"/>
     </row>
     <row r="64" ht="27.75" customHeight="1">
-      <c r="A64" s="64" t="s">
-        <v>105</v>
-      </c>
-      <c r="B64" s="60">
-        <f t="shared" ref="B64:D64" si="5">$G$58*B62</f>
-        <v>957.008</v>
-      </c>
-      <c r="C64" s="60">
-        <f t="shared" si="5"/>
-        <v>1339.8112</v>
-      </c>
-      <c r="D64" s="60">
-        <f t="shared" si="5"/>
-        <v>133.98112</v>
-      </c>
+      <c r="A64" s="1"/>
+      <c r="B64" s="1"/>
+      <c r="C64" s="1"/>
+      <c r="D64" s="2"/>
       <c r="E64" s="3"/>
       <c r="F64" s="1"/>
       <c r="G64" s="1"/>
@@ -3897,21 +3882,10 @@
       <c r="Z64" s="1"/>
     </row>
     <row r="65" ht="27.75" customHeight="1">
-      <c r="A65" s="64" t="s">
-        <v>106</v>
-      </c>
-      <c r="B65" s="65">
-        <f t="shared" ref="B65:C65" si="6">B64/(22*8)</f>
-        <v>5.437545455</v>
-      </c>
-      <c r="C65" s="65">
-        <f t="shared" si="6"/>
-        <v>7.612563636</v>
-      </c>
-      <c r="D65" s="66">
-        <f>D64/(22*3)</f>
-        <v>2.03001697</v>
-      </c>
+      <c r="A65" s="1"/>
+      <c r="B65" s="1"/>
+      <c r="C65" s="1"/>
+      <c r="D65" s="1"/>
       <c r="E65" s="3"/>
       <c r="F65" s="1"/>
       <c r="G65" s="1"/>
@@ -3936,12 +3910,16 @@
       <c r="Z65" s="1"/>
     </row>
     <row r="66" ht="27.75" customHeight="1">
-      <c r="A66" s="1"/>
-      <c r="B66" s="1"/>
-      <c r="C66" s="1"/>
-      <c r="D66" s="2"/>
-      <c r="E66" s="3"/>
-      <c r="F66" s="1"/>
+      <c r="A66" s="18" t="s">
+        <v>105</v>
+      </c>
+      <c r="B66" s="67" t="s">
+        <v>106</v>
+      </c>
+      <c r="C66" s="68"/>
+      <c r="D66" s="55"/>
+      <c r="E66" s="54"/>
+      <c r="F66" s="69"/>
       <c r="G66" s="1"/>
       <c r="H66" s="1"/>
       <c r="I66" s="1"/>
@@ -3965,11 +3943,21 @@
     </row>
     <row r="67" ht="27.75" customHeight="1">
       <c r="A67" s="1"/>
-      <c r="B67" s="1"/>
-      <c r="C67" s="1"/>
-      <c r="D67" s="1"/>
-      <c r="E67" s="3"/>
-      <c r="F67" s="1"/>
+      <c r="B67" s="43" t="s">
+        <v>107</v>
+      </c>
+      <c r="C67" s="19" t="s">
+        <v>108</v>
+      </c>
+      <c r="D67" s="58" t="s">
+        <v>109</v>
+      </c>
+      <c r="E67" s="58" t="s">
+        <v>110</v>
+      </c>
+      <c r="F67" s="58" t="s">
+        <v>111</v>
+      </c>
       <c r="G67" s="1"/>
       <c r="H67" s="1"/>
       <c r="I67" s="1"/>
@@ -3992,16 +3980,25 @@
       <c r="Z67" s="1"/>
     </row>
     <row r="68" ht="27.75" customHeight="1">
-      <c r="A68" s="18" t="s">
-        <v>107</v>
-      </c>
-      <c r="B68" s="67" t="s">
-        <v>108</v>
-      </c>
-      <c r="C68" s="68"/>
-      <c r="D68" s="55"/>
-      <c r="E68" s="54"/>
-      <c r="F68" s="69"/>
+      <c r="A68" s="1"/>
+      <c r="B68" s="70" t="s">
+        <v>112</v>
+      </c>
+      <c r="C68" s="71">
+        <v>0.4</v>
+      </c>
+      <c r="D68" s="65">
+        <f t="shared" ref="D68:F68" si="5">$C68/$C$68*B$63</f>
+        <v>3.540727273</v>
+      </c>
+      <c r="E68" s="65">
+        <f t="shared" si="5"/>
+        <v>4.957018182</v>
+      </c>
+      <c r="F68" s="65">
+        <f t="shared" si="5"/>
+        <v>1.321871515</v>
+      </c>
       <c r="G68" s="1"/>
       <c r="H68" s="1"/>
       <c r="I68" s="1"/>
@@ -4025,20 +4022,24 @@
     </row>
     <row r="69" ht="27.75" customHeight="1">
       <c r="A69" s="1"/>
-      <c r="B69" s="43" t="s">
-        <v>109</v>
-      </c>
-      <c r="C69" s="19" t="s">
-        <v>110</v>
-      </c>
-      <c r="D69" s="58" t="s">
-        <v>111</v>
-      </c>
-      <c r="E69" s="58" t="s">
-        <v>112</v>
-      </c>
-      <c r="F69" s="58" t="s">
+      <c r="B69" s="70" t="s">
         <v>113</v>
+      </c>
+      <c r="C69" s="71">
+        <f>1-C68</f>
+        <v>0.6</v>
+      </c>
+      <c r="D69" s="60">
+        <f t="shared" ref="D69:F69" si="6">$C69/$C$68*B$63</f>
+        <v>5.311090909</v>
+      </c>
+      <c r="E69" s="60">
+        <f t="shared" si="6"/>
+        <v>7.435527273</v>
+      </c>
+      <c r="F69" s="60">
+        <f t="shared" si="6"/>
+        <v>1.982807273</v>
       </c>
       <c r="G69" s="1"/>
       <c r="H69" s="1"/>
@@ -4063,23 +4064,22 @@
     </row>
     <row r="70" ht="27.75" customHeight="1">
       <c r="A70" s="1"/>
-      <c r="B70" s="70" t="s">
-        <v>114</v>
-      </c>
+      <c r="B70" s="72"/>
       <c r="C70" s="71">
-        <v>0.4</v>
+        <f>SUM(C68:C69)</f>
+        <v>1</v>
       </c>
       <c r="D70" s="65">
-        <f t="shared" ref="D70:F70" si="7">$C70/$C$70*B$65</f>
-        <v>5.437545455</v>
+        <f t="shared" ref="D70:F70" si="7">$C70/$C$68*B$63</f>
+        <v>8.851818182</v>
       </c>
       <c r="E70" s="65">
         <f t="shared" si="7"/>
-        <v>7.612563636</v>
+        <v>12.39254545</v>
       </c>
       <c r="F70" s="65">
         <f t="shared" si="7"/>
-        <v>2.03001697</v>
+        <v>3.304678788</v>
       </c>
       <c r="G70" s="1"/>
       <c r="H70" s="1"/>
@@ -4104,25 +4104,11 @@
     </row>
     <row r="71" ht="27.75" customHeight="1">
       <c r="A71" s="1"/>
-      <c r="B71" s="70" t="s">
-        <v>115</v>
-      </c>
-      <c r="C71" s="71">
-        <f>1-C70</f>
-        <v>0.6</v>
-      </c>
-      <c r="D71" s="60">
-        <f t="shared" ref="D71:F71" si="8">$C71/$C$70*B$65</f>
-        <v>8.156318182</v>
-      </c>
-      <c r="E71" s="60">
-        <f t="shared" si="8"/>
-        <v>11.41884545</v>
-      </c>
-      <c r="F71" s="60">
-        <f t="shared" si="8"/>
-        <v>3.045025455</v>
-      </c>
+      <c r="B71" s="1"/>
+      <c r="C71" s="1"/>
+      <c r="D71" s="2"/>
+      <c r="E71" s="3"/>
+      <c r="F71" s="1"/>
       <c r="G71" s="1"/>
       <c r="H71" s="1"/>
       <c r="I71" s="1"/>
@@ -4145,24 +4131,16 @@
       <c r="Z71" s="1"/>
     </row>
     <row r="72" ht="27.75" customHeight="1">
-      <c r="A72" s="1"/>
-      <c r="B72" s="72"/>
-      <c r="C72" s="71">
-        <f>SUM(C70:C71)</f>
-        <v>1</v>
-      </c>
-      <c r="D72" s="65">
-        <f t="shared" ref="D72:F72" si="9">$C72/$C$70*B$65</f>
-        <v>13.59386364</v>
-      </c>
-      <c r="E72" s="65">
-        <f t="shared" si="9"/>
-        <v>19.03140909</v>
-      </c>
-      <c r="F72" s="65">
-        <f t="shared" si="9"/>
-        <v>5.075042424</v>
-      </c>
+      <c r="A72" s="18" t="s">
+        <v>114</v>
+      </c>
+      <c r="B72" s="25">
+        <v>5.0</v>
+      </c>
+      <c r="C72" s="1"/>
+      <c r="D72" s="2"/>
+      <c r="E72" s="3"/>
+      <c r="F72" s="1"/>
       <c r="G72" s="1"/>
       <c r="H72" s="1"/>
       <c r="I72" s="1"/>
@@ -4214,13 +4192,17 @@
     </row>
     <row r="74" ht="27.75" customHeight="1">
       <c r="A74" s="18" t="s">
+        <v>115</v>
+      </c>
+      <c r="B74" s="58" t="s">
         <v>116</v>
       </c>
-      <c r="B74" s="25">
-        <v>5.0</v>
-      </c>
-      <c r="C74" s="1"/>
-      <c r="D74" s="2"/>
+      <c r="C74" s="58" t="s">
+        <v>117</v>
+      </c>
+      <c r="D74" s="58" t="s">
+        <v>118</v>
+      </c>
       <c r="E74" s="3"/>
       <c r="F74" s="1"/>
       <c r="G74" s="1"/>
@@ -4245,13 +4227,22 @@
       <c r="Z74" s="1"/>
     </row>
     <row r="75" ht="27.75" customHeight="1">
-      <c r="A75" s="1"/>
-      <c r="B75" s="1"/>
-      <c r="C75" s="1"/>
-      <c r="D75" s="2"/>
-      <c r="E75" s="3"/>
-      <c r="F75" s="1"/>
-      <c r="G75" s="1"/>
+      <c r="A75" s="73"/>
+      <c r="B75" s="74">
+        <f>$D$70/$B$72</f>
+        <v>1.770363636</v>
+      </c>
+      <c r="C75" s="74">
+        <f>$E$70/$B$72</f>
+        <v>2.478509091</v>
+      </c>
+      <c r="D75" s="74">
+        <f>$F$70/$B$72</f>
+        <v>0.6609357576</v>
+      </c>
+      <c r="E75" s="73"/>
+      <c r="F75" s="73"/>
+      <c r="G75" s="73"/>
       <c r="H75" s="1"/>
       <c r="I75" s="1"/>
       <c r="J75" s="1"/>
@@ -4273,79 +4264,62 @@
       <c r="Z75" s="1"/>
     </row>
     <row r="76" ht="27.75" customHeight="1">
-      <c r="A76" s="18" t="s">
-        <v>117</v>
-      </c>
-      <c r="B76" s="58" t="s">
-        <v>118</v>
-      </c>
-      <c r="C76" s="58" t="s">
-        <v>119</v>
-      </c>
-      <c r="D76" s="58" t="s">
-        <v>120</v>
-      </c>
-      <c r="E76" s="3"/>
-      <c r="F76" s="1"/>
-      <c r="G76" s="1"/>
-      <c r="H76" s="1"/>
-      <c r="I76" s="1"/>
-      <c r="J76" s="1"/>
-      <c r="K76" s="1"/>
-      <c r="L76" s="1"/>
-      <c r="M76" s="1"/>
-      <c r="N76" s="1"/>
-      <c r="O76" s="1"/>
-      <c r="P76" s="1"/>
-      <c r="Q76" s="1"/>
-      <c r="R76" s="1"/>
-      <c r="S76" s="1"/>
-      <c r="T76" s="1"/>
-      <c r="U76" s="1"/>
-      <c r="V76" s="1"/>
-      <c r="W76" s="1"/>
-      <c r="X76" s="1"/>
-      <c r="Y76" s="1"/>
-      <c r="Z76" s="1"/>
-    </row>
-    <row r="77" ht="27.75" customHeight="1">
+      <c r="A76" s="73"/>
+      <c r="B76" s="73"/>
+      <c r="C76" s="73"/>
+      <c r="D76" s="73"/>
+      <c r="E76" s="75"/>
+      <c r="F76" s="73"/>
+      <c r="G76" s="73"/>
+      <c r="H76" s="73"/>
+      <c r="I76" s="73"/>
+      <c r="J76" s="73"/>
+      <c r="K76" s="73"/>
+      <c r="L76" s="73"/>
+      <c r="M76" s="73"/>
+      <c r="N76" s="73"/>
+      <c r="O76" s="73"/>
+      <c r="P76" s="73"/>
+      <c r="Q76" s="73"/>
+      <c r="R76" s="73"/>
+      <c r="S76" s="73"/>
+      <c r="T76" s="73"/>
+      <c r="U76" s="73"/>
+      <c r="V76" s="73"/>
+      <c r="W76" s="73"/>
+      <c r="X76" s="73"/>
+      <c r="Y76" s="73"/>
+      <c r="Z76" s="73"/>
+    </row>
+    <row r="77" ht="15.75" customHeight="1">
       <c r="A77" s="73"/>
-      <c r="B77" s="74">
-        <f>$D$72/$B$74</f>
-        <v>2.718772727</v>
-      </c>
-      <c r="C77" s="74">
-        <f>$E$72/$B$74</f>
-        <v>3.806281818</v>
-      </c>
-      <c r="D77" s="74">
-        <f>$F$72/$B$74</f>
-        <v>1.015008485</v>
-      </c>
-      <c r="E77" s="73"/>
+      <c r="B77" s="73"/>
+      <c r="C77" s="73"/>
+      <c r="D77" s="73"/>
+      <c r="E77" s="75"/>
       <c r="F77" s="73"/>
       <c r="G77" s="73"/>
-      <c r="H77" s="1"/>
-      <c r="I77" s="1"/>
-      <c r="J77" s="1"/>
-      <c r="K77" s="1"/>
-      <c r="L77" s="1"/>
-      <c r="M77" s="1"/>
-      <c r="N77" s="1"/>
-      <c r="O77" s="1"/>
-      <c r="P77" s="1"/>
-      <c r="Q77" s="1"/>
-      <c r="R77" s="1"/>
-      <c r="S77" s="1"/>
-      <c r="T77" s="1"/>
-      <c r="U77" s="1"/>
-      <c r="V77" s="1"/>
-      <c r="W77" s="1"/>
-      <c r="X77" s="1"/>
-      <c r="Y77" s="1"/>
-      <c r="Z77" s="1"/>
-    </row>
-    <row r="78" ht="27.75" customHeight="1">
+      <c r="H77" s="73"/>
+      <c r="I77" s="73"/>
+      <c r="J77" s="73"/>
+      <c r="K77" s="73"/>
+      <c r="L77" s="73"/>
+      <c r="M77" s="73"/>
+      <c r="N77" s="73"/>
+      <c r="O77" s="73"/>
+      <c r="P77" s="73"/>
+      <c r="Q77" s="73"/>
+      <c r="R77" s="73"/>
+      <c r="S77" s="73"/>
+      <c r="T77" s="73"/>
+      <c r="U77" s="73"/>
+      <c r="V77" s="73"/>
+      <c r="W77" s="73"/>
+      <c r="X77" s="73"/>
+      <c r="Y77" s="73"/>
+      <c r="Z77" s="73"/>
+    </row>
+    <row r="78" ht="15.75" customHeight="1">
       <c r="A78" s="73"/>
       <c r="B78" s="73"/>
       <c r="C78" s="73"/>
@@ -4738,13 +4712,13 @@
       <c r="Z91" s="73"/>
     </row>
     <row r="92" ht="15.75" customHeight="1">
-      <c r="A92" s="73"/>
-      <c r="B92" s="73"/>
-      <c r="C92" s="73"/>
-      <c r="D92" s="73"/>
-      <c r="E92" s="75"/>
-      <c r="F92" s="73"/>
-      <c r="G92" s="73"/>
+      <c r="A92" s="1"/>
+      <c r="B92" s="1"/>
+      <c r="C92" s="1"/>
+      <c r="D92" s="2"/>
+      <c r="E92" s="3"/>
+      <c r="F92" s="1"/>
+      <c r="G92" s="1"/>
       <c r="H92" s="73"/>
       <c r="I92" s="73"/>
       <c r="J92" s="73"/>
@@ -4766,32 +4740,32 @@
       <c r="Z92" s="73"/>
     </row>
     <row r="93" ht="15.75" customHeight="1">
-      <c r="A93" s="73"/>
-      <c r="B93" s="73"/>
-      <c r="C93" s="73"/>
-      <c r="D93" s="73"/>
-      <c r="E93" s="75"/>
-      <c r="F93" s="73"/>
-      <c r="G93" s="73"/>
-      <c r="H93" s="73"/>
-      <c r="I93" s="73"/>
-      <c r="J93" s="73"/>
-      <c r="K93" s="73"/>
-      <c r="L93" s="73"/>
-      <c r="M93" s="73"/>
-      <c r="N93" s="73"/>
-      <c r="O93" s="73"/>
-      <c r="P93" s="73"/>
-      <c r="Q93" s="73"/>
-      <c r="R93" s="73"/>
-      <c r="S93" s="73"/>
-      <c r="T93" s="73"/>
-      <c r="U93" s="73"/>
-      <c r="V93" s="73"/>
-      <c r="W93" s="73"/>
-      <c r="X93" s="73"/>
-      <c r="Y93" s="73"/>
-      <c r="Z93" s="73"/>
+      <c r="A93" s="1"/>
+      <c r="B93" s="1"/>
+      <c r="C93" s="1"/>
+      <c r="D93" s="2"/>
+      <c r="E93" s="3"/>
+      <c r="F93" s="1"/>
+      <c r="G93" s="1"/>
+      <c r="H93" s="1"/>
+      <c r="I93" s="1"/>
+      <c r="J93" s="1"/>
+      <c r="K93" s="1"/>
+      <c r="L93" s="1"/>
+      <c r="M93" s="1"/>
+      <c r="N93" s="1"/>
+      <c r="O93" s="1"/>
+      <c r="P93" s="1"/>
+      <c r="Q93" s="1"/>
+      <c r="R93" s="1"/>
+      <c r="S93" s="1"/>
+      <c r="T93" s="1"/>
+      <c r="U93" s="1"/>
+      <c r="V93" s="1"/>
+      <c r="W93" s="1"/>
+      <c r="X93" s="1"/>
+      <c r="Y93" s="1"/>
+      <c r="Z93" s="1"/>
     </row>
     <row r="94" ht="15.75" customHeight="1">
       <c r="A94" s="1"/>
@@ -4801,25 +4775,25 @@
       <c r="E94" s="3"/>
       <c r="F94" s="1"/>
       <c r="G94" s="1"/>
-      <c r="H94" s="73"/>
-      <c r="I94" s="73"/>
-      <c r="J94" s="73"/>
-      <c r="K94" s="73"/>
-      <c r="L94" s="73"/>
-      <c r="M94" s="73"/>
-      <c r="N94" s="73"/>
-      <c r="O94" s="73"/>
-      <c r="P94" s="73"/>
-      <c r="Q94" s="73"/>
-      <c r="R94" s="73"/>
-      <c r="S94" s="73"/>
-      <c r="T94" s="73"/>
-      <c r="U94" s="73"/>
-      <c r="V94" s="73"/>
-      <c r="W94" s="73"/>
-      <c r="X94" s="73"/>
-      <c r="Y94" s="73"/>
-      <c r="Z94" s="73"/>
+      <c r="H94" s="1"/>
+      <c r="I94" s="1"/>
+      <c r="J94" s="1"/>
+      <c r="K94" s="1"/>
+      <c r="L94" s="1"/>
+      <c r="M94" s="1"/>
+      <c r="N94" s="1"/>
+      <c r="O94" s="1"/>
+      <c r="P94" s="1"/>
+      <c r="Q94" s="1"/>
+      <c r="R94" s="1"/>
+      <c r="S94" s="1"/>
+      <c r="T94" s="1"/>
+      <c r="U94" s="1"/>
+      <c r="V94" s="1"/>
+      <c r="W94" s="1"/>
+      <c r="X94" s="1"/>
+      <c r="Y94" s="1"/>
+      <c r="Z94" s="1"/>
     </row>
     <row r="95" ht="15.75" customHeight="1">
       <c r="A95" s="1"/>
@@ -9889,62 +9863,8 @@
       <c r="Y275" s="1"/>
       <c r="Z275" s="1"/>
     </row>
-    <row r="276" ht="15.75" customHeight="1">
-      <c r="A276" s="1"/>
-      <c r="B276" s="1"/>
-      <c r="C276" s="1"/>
-      <c r="D276" s="2"/>
-      <c r="E276" s="3"/>
-      <c r="F276" s="1"/>
-      <c r="G276" s="1"/>
-      <c r="H276" s="1"/>
-      <c r="I276" s="1"/>
-      <c r="J276" s="1"/>
-      <c r="K276" s="1"/>
-      <c r="L276" s="1"/>
-      <c r="M276" s="1"/>
-      <c r="N276" s="1"/>
-      <c r="O276" s="1"/>
-      <c r="P276" s="1"/>
-      <c r="Q276" s="1"/>
-      <c r="R276" s="1"/>
-      <c r="S276" s="1"/>
-      <c r="T276" s="1"/>
-      <c r="U276" s="1"/>
-      <c r="V276" s="1"/>
-      <c r="W276" s="1"/>
-      <c r="X276" s="1"/>
-      <c r="Y276" s="1"/>
-      <c r="Z276" s="1"/>
-    </row>
-    <row r="277" ht="15.75" customHeight="1">
-      <c r="A277" s="1"/>
-      <c r="B277" s="1"/>
-      <c r="C277" s="1"/>
-      <c r="D277" s="2"/>
-      <c r="E277" s="3"/>
-      <c r="F277" s="1"/>
-      <c r="G277" s="1"/>
-      <c r="H277" s="1"/>
-      <c r="I277" s="1"/>
-      <c r="J277" s="1"/>
-      <c r="K277" s="1"/>
-      <c r="L277" s="1"/>
-      <c r="M277" s="1"/>
-      <c r="N277" s="1"/>
-      <c r="O277" s="1"/>
-      <c r="P277" s="1"/>
-      <c r="Q277" s="1"/>
-      <c r="R277" s="1"/>
-      <c r="S277" s="1"/>
-      <c r="T277" s="1"/>
-      <c r="U277" s="1"/>
-      <c r="V277" s="1"/>
-      <c r="W277" s="1"/>
-      <c r="X277" s="1"/>
-      <c r="Y277" s="1"/>
-      <c r="Z277" s="1"/>
-    </row>
+    <row r="276" ht="15.75" customHeight="1"/>
+    <row r="277" ht="15.75" customHeight="1"/>
     <row r="278" ht="15.75" customHeight="1"/>
     <row r="279" ht="15.75" customHeight="1"/>
     <row r="280" ht="15.75" customHeight="1"/>
@@ -10656,33 +10576,31 @@
     <row r="986" ht="15.75" customHeight="1"/>
     <row r="987" ht="15.75" customHeight="1"/>
     <row r="988" ht="15.75" customHeight="1"/>
-    <row r="989" ht="15.75" customHeight="1"/>
-    <row r="990" ht="15.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="10">
-    <mergeCell ref="B54:F54"/>
-    <mergeCell ref="B58:F58"/>
-    <mergeCell ref="B63:D63"/>
+    <mergeCell ref="B52:F52"/>
+    <mergeCell ref="B56:F56"/>
+    <mergeCell ref="B61:D61"/>
     <mergeCell ref="B2:G2"/>
     <mergeCell ref="C11:F11"/>
-    <mergeCell ref="C20:E20"/>
-    <mergeCell ref="C23:E23"/>
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B41:F41"/>
-    <mergeCell ref="B53:F53"/>
+    <mergeCell ref="C18:E18"/>
+    <mergeCell ref="C21:E21"/>
+    <mergeCell ref="B38:F38"/>
+    <mergeCell ref="B39:F39"/>
+    <mergeCell ref="B51:F51"/>
   </mergeCells>
   <dataValidations>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="C8:C10">
       <formula1>"Simple,Intermedio,Complejo"</formula1>
     </dataValidation>
-    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Entre 1 y 9 personas." sqref="B74">
+    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Entre 1 y 9 personas." sqref="B72">
       <formula1>1.0</formula1>
       <formula2>9.0</formula2>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink r:id="rId2" location="v=onepage&amp;q=e7%20part-time%20members&amp;f=false" ref="H28"/>
-    <hyperlink r:id="rId3" location="v=onepage&amp;q=e7%20part-time%20members&amp;f=false" ref="H46"/>
+    <hyperlink r:id="rId2" location="v=onepage&amp;q=e7%20part-time%20members&amp;f=false" ref="H26"/>
+    <hyperlink r:id="rId3" location="v=onepage&amp;q=e7%20part-time%20members&amp;f=false" ref="H44"/>
   </hyperlinks>
   <printOptions/>
   <pageMargins bottom="1.0" footer="0.0" header="0.0" left="0.75" right="0.75" top="1.0"/>

--- a/Etapa Construcción - Iteración 1/ESTIMACION DE CU.xlsx
+++ b/Etapa Construcción - Iteración 1/ESTIMACION DE CU.xlsx
@@ -268,7 +268,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="121">
   <si>
     <t>ESTIMACIÓN por PUNTOS de CASO de USO</t>
   </si>
@@ -343,6 +343,12 @@
   </si>
   <si>
     <t>Complejidad</t>
+  </si>
+  <si>
+    <t>CU01:  Iniciar sesión</t>
+  </si>
+  <si>
+    <t>Simple</t>
   </si>
   <si>
     <t>CU##: Gestionar tareas</t>
@@ -936,7 +942,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="76">
+  <cellXfs count="78">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -1036,7 +1042,13 @@
       <alignment horizontal="right" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="9" fillId="3" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment readingOrder="0" vertical="center"/>
+    </xf>
+    <xf borderId="9" fillId="3" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
+    </xf>
+    <xf borderId="9" fillId="4" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="49" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment vertical="center"/>
@@ -2072,11 +2084,19 @@
     </row>
     <row r="15" ht="27.75" customHeight="1">
       <c r="A15" s="1"/>
-      <c r="B15" s="21"/>
+      <c r="B15" s="34" t="s">
+        <v>25</v>
+      </c>
       <c r="C15" s="21"/>
-      <c r="D15" s="34"/>
-      <c r="E15" s="24"/>
-      <c r="F15" s="24"/>
+      <c r="D15" s="35">
+        <v>2.0</v>
+      </c>
+      <c r="E15" s="36" t="s">
+        <v>26</v>
+      </c>
+      <c r="F15" s="36">
+        <v>5.0</v>
+      </c>
       <c r="G15" s="1"/>
       <c r="H15" s="17"/>
       <c r="I15" s="1"/>
@@ -2090,7 +2110,7 @@
       <c r="Q15" s="1"/>
       <c r="R15" s="1"/>
       <c r="S15" s="1"/>
-      <c r="T15" s="35"/>
+      <c r="T15" s="37"/>
       <c r="U15" s="1"/>
       <c r="V15" s="1"/>
       <c r="W15" s="1"/>
@@ -2101,10 +2121,10 @@
     <row r="16" ht="27.75" customHeight="1">
       <c r="A16" s="1"/>
       <c r="B16" s="21" t="s">
-        <v>25</v>
-      </c>
-      <c r="C16" s="36"/>
-      <c r="D16" s="37">
+        <v>27</v>
+      </c>
+      <c r="C16" s="38"/>
+      <c r="D16" s="39">
         <v>10.0</v>
       </c>
       <c r="E16" s="24" t="str">
@@ -2119,7 +2139,7 @@
       <c r="H16" s="1"/>
       <c r="I16" s="1"/>
       <c r="J16" s="1"/>
-      <c r="K16" s="35"/>
+      <c r="K16" s="37"/>
       <c r="L16" s="1"/>
       <c r="M16" s="1"/>
       <c r="N16" s="1"/>
@@ -2128,7 +2148,7 @@
       <c r="Q16" s="1"/>
       <c r="R16" s="1"/>
       <c r="S16" s="1"/>
-      <c r="T16" s="35"/>
+      <c r="T16" s="37"/>
       <c r="U16" s="1"/>
       <c r="V16" s="1"/>
       <c r="W16" s="1"/>
@@ -2139,14 +2159,14 @@
     <row r="17" ht="27.75" customHeight="1">
       <c r="A17" s="1"/>
       <c r="B17" s="21" t="s">
-        <v>26</v>
-      </c>
-      <c r="C17" s="36"/>
-      <c r="D17" s="37">
+        <v>28</v>
+      </c>
+      <c r="C17" s="38"/>
+      <c r="D17" s="39">
         <v>4.0</v>
       </c>
       <c r="E17" s="24" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F17" s="24">
         <v>10.0</v>
@@ -2155,7 +2175,7 @@
       <c r="H17" s="1"/>
       <c r="I17" s="1"/>
       <c r="J17" s="1"/>
-      <c r="K17" s="35"/>
+      <c r="K17" s="37"/>
       <c r="L17" s="1"/>
       <c r="M17" s="1"/>
       <c r="N17" s="1"/>
@@ -2164,7 +2184,7 @@
       <c r="Q17" s="1"/>
       <c r="R17" s="1"/>
       <c r="S17" s="1"/>
-      <c r="T17" s="35"/>
+      <c r="T17" s="37"/>
       <c r="U17" s="1"/>
       <c r="V17" s="1"/>
       <c r="W17" s="1"/>
@@ -2174,21 +2194,21 @@
     </row>
     <row r="18" ht="27.75" customHeight="1">
       <c r="A18" s="1"/>
-      <c r="B18" s="38"/>
-      <c r="C18" s="39" t="s">
-        <v>28</v>
-      </c>
-      <c r="D18" s="40"/>
-      <c r="E18" s="41"/>
-      <c r="F18" s="42">
+      <c r="B18" s="40"/>
+      <c r="C18" s="41" t="s">
+        <v>30</v>
+      </c>
+      <c r="D18" s="42"/>
+      <c r="E18" s="43"/>
+      <c r="F18" s="44">
         <f>SUM(F15:F17)</f>
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="G18" s="1"/>
       <c r="H18" s="1"/>
       <c r="I18" s="1"/>
       <c r="J18" s="1"/>
-      <c r="K18" s="35"/>
+      <c r="K18" s="37"/>
       <c r="L18" s="1"/>
       <c r="M18" s="1"/>
       <c r="N18" s="1"/>
@@ -2197,7 +2217,7 @@
       <c r="Q18" s="1"/>
       <c r="R18" s="1"/>
       <c r="S18" s="1"/>
-      <c r="T18" s="35"/>
+      <c r="T18" s="37"/>
       <c r="U18" s="1"/>
       <c r="V18" s="1"/>
       <c r="W18" s="1"/>
@@ -2216,7 +2236,7 @@
       <c r="H19" s="18"/>
       <c r="I19" s="1"/>
       <c r="J19" s="1"/>
-      <c r="K19" s="35"/>
+      <c r="K19" s="37"/>
       <c r="L19" s="1"/>
       <c r="M19" s="1"/>
       <c r="N19" s="1"/>
@@ -2263,17 +2283,17 @@
     </row>
     <row r="21" ht="27.75" customHeight="1">
       <c r="A21" s="18" t="s">
-        <v>29</v>
-      </c>
-      <c r="B21" s="43"/>
+        <v>31</v>
+      </c>
+      <c r="B21" s="45"/>
       <c r="C21" s="28" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D21" s="6"/>
       <c r="E21" s="7"/>
       <c r="F21" s="29">
         <f>G11+F18</f>
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="G21" s="1"/>
       <c r="H21" s="1"/>
@@ -2354,25 +2374,25 @@
     </row>
     <row r="24" ht="27.75" customHeight="1">
       <c r="A24" s="18" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B24" s="20" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C24" s="20" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D24" s="19" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E24" s="19" t="s">
         <v>9</v>
       </c>
       <c r="F24" s="19" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G24" s="19" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="H24" s="1"/>
       <c r="I24" s="1"/>
@@ -2396,27 +2416,27 @@
     </row>
     <row r="25" ht="27.75" customHeight="1">
       <c r="A25" s="1"/>
-      <c r="B25" s="44" t="s">
-        <v>37</v>
-      </c>
-      <c r="C25" s="44" t="s">
-        <v>38</v>
-      </c>
-      <c r="D25" s="45" t="s">
+      <c r="B25" s="46" t="s">
         <v>39</v>
       </c>
-      <c r="E25" s="46">
+      <c r="C25" s="46" t="s">
+        <v>40</v>
+      </c>
+      <c r="D25" s="47" t="s">
+        <v>41</v>
+      </c>
+      <c r="E25" s="48">
         <v>2.0</v>
       </c>
       <c r="F25" s="25">
         <v>0.0</v>
       </c>
-      <c r="G25" s="47">
+      <c r="G25" s="49">
         <f t="shared" ref="G25:G37" si="1">E25*F25</f>
         <v>0</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="I25" s="18"/>
       <c r="J25" s="18"/>
@@ -2439,27 +2459,27 @@
     </row>
     <row r="26" ht="27.75" customHeight="1">
       <c r="A26" s="1"/>
-      <c r="B26" s="44" t="s">
-        <v>41</v>
-      </c>
-      <c r="C26" s="44" t="s">
-        <v>38</v>
-      </c>
-      <c r="D26" s="48" t="s">
-        <v>42</v>
-      </c>
-      <c r="E26" s="47">
+      <c r="B26" s="46" t="s">
+        <v>43</v>
+      </c>
+      <c r="C26" s="46" t="s">
+        <v>40</v>
+      </c>
+      <c r="D26" s="50" t="s">
+        <v>44</v>
+      </c>
+      <c r="E26" s="49">
         <v>2.0</v>
       </c>
       <c r="F26" s="25">
         <v>5.0</v>
       </c>
-      <c r="G26" s="47">
+      <c r="G26" s="49">
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="H26" s="49" t="s">
-        <v>43</v>
+      <c r="H26" s="51" t="s">
+        <v>45</v>
       </c>
       <c r="I26" s="1"/>
       <c r="J26" s="1"/>
@@ -2482,20 +2502,20 @@
     </row>
     <row r="27" ht="27.0" customHeight="1">
       <c r="A27" s="1"/>
-      <c r="B27" s="44" t="s">
-        <v>44</v>
-      </c>
-      <c r="C27" s="44" t="s">
-        <v>38</v>
-      </c>
-      <c r="D27" s="48"/>
-      <c r="E27" s="47">
+      <c r="B27" s="46" t="s">
+        <v>46</v>
+      </c>
+      <c r="C27" s="46" t="s">
+        <v>40</v>
+      </c>
+      <c r="D27" s="50"/>
+      <c r="E27" s="49">
         <v>1.0</v>
       </c>
       <c r="F27" s="25">
         <v>5.0</v>
       </c>
-      <c r="G27" s="47">
+      <c r="G27" s="49">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
@@ -2521,22 +2541,22 @@
     </row>
     <row r="28" ht="27.75" customHeight="1">
       <c r="A28" s="1"/>
-      <c r="B28" s="44" t="s">
-        <v>45</v>
-      </c>
-      <c r="C28" s="44" t="s">
-        <v>38</v>
-      </c>
-      <c r="D28" s="45" t="s">
-        <v>46</v>
-      </c>
-      <c r="E28" s="47">
+      <c r="B28" s="46" t="s">
+        <v>47</v>
+      </c>
+      <c r="C28" s="46" t="s">
+        <v>40</v>
+      </c>
+      <c r="D28" s="47" t="s">
+        <v>48</v>
+      </c>
+      <c r="E28" s="49">
         <v>1.0</v>
       </c>
       <c r="F28" s="25">
         <v>3.0</v>
       </c>
-      <c r="G28" s="47">
+      <c r="G28" s="49">
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
@@ -2562,22 +2582,22 @@
     </row>
     <row r="29" ht="30.75" customHeight="1">
       <c r="A29" s="1"/>
-      <c r="B29" s="44" t="s">
-        <v>47</v>
-      </c>
-      <c r="C29" s="44" t="s">
-        <v>38</v>
-      </c>
-      <c r="D29" s="45" t="s">
-        <v>48</v>
-      </c>
-      <c r="E29" s="46">
+      <c r="B29" s="46" t="s">
+        <v>49</v>
+      </c>
+      <c r="C29" s="46" t="s">
+        <v>40</v>
+      </c>
+      <c r="D29" s="47" t="s">
+        <v>50</v>
+      </c>
+      <c r="E29" s="48">
         <v>1.0</v>
       </c>
       <c r="F29" s="25">
         <v>0.0</v>
       </c>
-      <c r="G29" s="47">
+      <c r="G29" s="49">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -2603,22 +2623,22 @@
     </row>
     <row r="30" ht="27.75" customHeight="1">
       <c r="A30" s="1"/>
-      <c r="B30" s="44" t="s">
-        <v>49</v>
-      </c>
-      <c r="C30" s="44" t="s">
-        <v>38</v>
-      </c>
-      <c r="D30" s="48" t="s">
-        <v>50</v>
-      </c>
-      <c r="E30" s="46">
+      <c r="B30" s="46" t="s">
+        <v>51</v>
+      </c>
+      <c r="C30" s="46" t="s">
+        <v>40</v>
+      </c>
+      <c r="D30" s="50" t="s">
+        <v>52</v>
+      </c>
+      <c r="E30" s="48">
         <v>0.5</v>
       </c>
       <c r="F30" s="25">
         <v>3.0</v>
       </c>
-      <c r="G30" s="47">
+      <c r="G30" s="49">
         <f t="shared" si="1"/>
         <v>1.5</v>
       </c>
@@ -2644,22 +2664,22 @@
     </row>
     <row r="31" ht="27.75" customHeight="1">
       <c r="A31" s="1"/>
-      <c r="B31" s="44" t="s">
-        <v>51</v>
-      </c>
-      <c r="C31" s="44" t="s">
-        <v>38</v>
-      </c>
-      <c r="D31" s="48" t="s">
-        <v>52</v>
-      </c>
-      <c r="E31" s="46">
+      <c r="B31" s="46" t="s">
+        <v>53</v>
+      </c>
+      <c r="C31" s="46" t="s">
+        <v>40</v>
+      </c>
+      <c r="D31" s="50" t="s">
+        <v>54</v>
+      </c>
+      <c r="E31" s="48">
         <v>0.5</v>
       </c>
       <c r="F31" s="25">
         <v>5.0</v>
       </c>
-      <c r="G31" s="47">
+      <c r="G31" s="49">
         <f t="shared" si="1"/>
         <v>2.5</v>
       </c>
@@ -2685,22 +2705,22 @@
     </row>
     <row r="32" ht="27.75" customHeight="1">
       <c r="A32" s="1"/>
-      <c r="B32" s="44" t="s">
-        <v>53</v>
-      </c>
-      <c r="C32" s="44" t="s">
-        <v>38</v>
-      </c>
-      <c r="D32" s="48" t="s">
-        <v>54</v>
-      </c>
-      <c r="E32" s="46">
+      <c r="B32" s="46" t="s">
+        <v>55</v>
+      </c>
+      <c r="C32" s="46" t="s">
+        <v>40</v>
+      </c>
+      <c r="D32" s="50" t="s">
+        <v>56</v>
+      </c>
+      <c r="E32" s="48">
         <v>2.0</v>
       </c>
       <c r="F32" s="25">
         <v>3.0</v>
       </c>
-      <c r="G32" s="47">
+      <c r="G32" s="49">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
@@ -2726,22 +2746,22 @@
     </row>
     <row r="33" ht="27.75" customHeight="1">
       <c r="A33" s="1"/>
-      <c r="B33" s="44" t="s">
-        <v>55</v>
-      </c>
-      <c r="C33" s="44" t="s">
-        <v>38</v>
-      </c>
-      <c r="D33" s="45" t="s">
-        <v>56</v>
-      </c>
-      <c r="E33" s="46">
+      <c r="B33" s="46" t="s">
+        <v>57</v>
+      </c>
+      <c r="C33" s="46" t="s">
+        <v>40</v>
+      </c>
+      <c r="D33" s="47" t="s">
+        <v>58</v>
+      </c>
+      <c r="E33" s="48">
         <v>1.0</v>
       </c>
       <c r="F33" s="25">
         <v>0.0</v>
       </c>
-      <c r="G33" s="47">
+      <c r="G33" s="49">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -2767,20 +2787,20 @@
     </row>
     <row r="34" ht="27.75" customHeight="1">
       <c r="A34" s="1"/>
-      <c r="B34" s="44" t="s">
-        <v>57</v>
-      </c>
-      <c r="C34" s="44" t="s">
-        <v>38</v>
-      </c>
-      <c r="D34" s="45"/>
-      <c r="E34" s="46">
+      <c r="B34" s="46" t="s">
+        <v>59</v>
+      </c>
+      <c r="C34" s="46" t="s">
+        <v>40</v>
+      </c>
+      <c r="D34" s="47"/>
+      <c r="E34" s="48">
         <v>1.0</v>
       </c>
       <c r="F34" s="25">
         <v>5.0</v>
       </c>
-      <c r="G34" s="47">
+      <c r="G34" s="49">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
@@ -2806,22 +2826,22 @@
     </row>
     <row r="35" ht="27.75" customHeight="1">
       <c r="A35" s="1"/>
-      <c r="B35" s="44" t="s">
-        <v>58</v>
-      </c>
-      <c r="C35" s="44" t="s">
-        <v>38</v>
-      </c>
-      <c r="D35" s="45" t="s">
-        <v>59</v>
-      </c>
-      <c r="E35" s="47">
+      <c r="B35" s="46" t="s">
+        <v>60</v>
+      </c>
+      <c r="C35" s="46" t="s">
+        <v>40</v>
+      </c>
+      <c r="D35" s="47" t="s">
+        <v>61</v>
+      </c>
+      <c r="E35" s="49">
         <v>1.0</v>
       </c>
       <c r="F35" s="25">
         <v>5.0</v>
       </c>
-      <c r="G35" s="47">
+      <c r="G35" s="49">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
@@ -2847,22 +2867,22 @@
     </row>
     <row r="36" ht="30.75" customHeight="1">
       <c r="A36" s="1"/>
-      <c r="B36" s="44" t="s">
-        <v>60</v>
-      </c>
-      <c r="C36" s="44" t="s">
-        <v>38</v>
-      </c>
-      <c r="D36" s="45" t="s">
-        <v>61</v>
-      </c>
-      <c r="E36" s="47">
+      <c r="B36" s="46" t="s">
+        <v>62</v>
+      </c>
+      <c r="C36" s="46" t="s">
+        <v>40</v>
+      </c>
+      <c r="D36" s="47" t="s">
+        <v>63</v>
+      </c>
+      <c r="E36" s="49">
         <v>1.0</v>
       </c>
       <c r="F36" s="25">
         <v>5.0</v>
       </c>
-      <c r="G36" s="47">
+      <c r="G36" s="49">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
@@ -2888,22 +2908,22 @@
     </row>
     <row r="37" ht="31.5" customHeight="1">
       <c r="A37" s="1"/>
-      <c r="B37" s="44" t="s">
-        <v>62</v>
-      </c>
-      <c r="C37" s="44" t="s">
-        <v>38</v>
-      </c>
-      <c r="D37" s="45" t="s">
-        <v>63</v>
-      </c>
-      <c r="E37" s="46">
+      <c r="B37" s="46" t="s">
+        <v>64</v>
+      </c>
+      <c r="C37" s="46" t="s">
+        <v>40</v>
+      </c>
+      <c r="D37" s="47" t="s">
+        <v>65</v>
+      </c>
+      <c r="E37" s="48">
         <v>1.0</v>
       </c>
       <c r="F37" s="25">
         <v>4.0</v>
       </c>
-      <c r="G37" s="47">
+      <c r="G37" s="49">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
@@ -2930,13 +2950,13 @@
     <row r="38" ht="30.75" customHeight="1">
       <c r="A38" s="1"/>
       <c r="B38" s="28" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C38" s="6"/>
       <c r="D38" s="6"/>
       <c r="E38" s="6"/>
       <c r="F38" s="7"/>
-      <c r="G38" s="50">
+      <c r="G38" s="52">
         <f>SUM(G25:G37)</f>
         <v>47</v>
       </c>
@@ -2963,13 +2983,13 @@
     <row r="39" ht="27.75" customHeight="1">
       <c r="A39" s="1"/>
       <c r="B39" s="28" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C39" s="6"/>
       <c r="D39" s="6"/>
       <c r="E39" s="6"/>
       <c r="F39" s="7"/>
-      <c r="G39" s="42">
+      <c r="G39" s="44">
         <f>0.6+(0.01*G38)</f>
         <v>1.07</v>
       </c>
@@ -3023,12 +3043,12 @@
     </row>
     <row r="41" ht="27.75" customHeight="1">
       <c r="A41" s="1"/>
-      <c r="B41" s="51"/>
-      <c r="C41" s="51"/>
-      <c r="D41" s="52"/>
-      <c r="E41" s="51"/>
-      <c r="F41" s="51"/>
-      <c r="G41" s="51"/>
+      <c r="B41" s="53"/>
+      <c r="C41" s="53"/>
+      <c r="D41" s="54"/>
+      <c r="E41" s="53"/>
+      <c r="F41" s="53"/>
+      <c r="G41" s="53"/>
       <c r="H41" s="1"/>
       <c r="I41" s="1"/>
       <c r="J41" s="1"/>
@@ -3051,25 +3071,25 @@
     </row>
     <row r="42" ht="27.75" customHeight="1">
       <c r="A42" s="18" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B42" s="20" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C42" s="20" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D42" s="19" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E42" s="19" t="s">
         <v>9</v>
       </c>
       <c r="F42" s="19" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G42" s="19" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="H42" s="1"/>
       <c r="I42" s="1"/>
@@ -3093,27 +3113,27 @@
     </row>
     <row r="43" ht="64.5" customHeight="1">
       <c r="A43" s="1"/>
-      <c r="B43" s="53" t="s">
-        <v>70</v>
-      </c>
-      <c r="C43" s="44" t="s">
-        <v>71</v>
-      </c>
-      <c r="D43" s="48" t="s">
+      <c r="B43" s="55" t="s">
         <v>72</v>
       </c>
-      <c r="E43" s="46">
+      <c r="C43" s="46" t="s">
+        <v>73</v>
+      </c>
+      <c r="D43" s="50" t="s">
+        <v>74</v>
+      </c>
+      <c r="E43" s="48">
         <v>1.5</v>
       </c>
       <c r="F43" s="25">
         <v>3.0</v>
       </c>
-      <c r="G43" s="47">
+      <c r="G43" s="49">
         <f t="shared" ref="G43:G50" si="2">E43*F43</f>
         <v>4.5</v>
       </c>
       <c r="H43" s="1" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="I43" s="18"/>
       <c r="J43" s="18"/>
@@ -3136,27 +3156,27 @@
     </row>
     <row r="44" ht="51.0" customHeight="1">
       <c r="A44" s="1"/>
-      <c r="B44" s="53" t="s">
-        <v>74</v>
-      </c>
-      <c r="C44" s="44" t="s">
-        <v>71</v>
-      </c>
-      <c r="D44" s="48" t="s">
-        <v>75</v>
-      </c>
-      <c r="E44" s="46">
+      <c r="B44" s="55" t="s">
+        <v>76</v>
+      </c>
+      <c r="C44" s="46" t="s">
+        <v>73</v>
+      </c>
+      <c r="D44" s="50" t="s">
+        <v>77</v>
+      </c>
+      <c r="E44" s="48">
         <v>0.5</v>
       </c>
       <c r="F44" s="25">
         <v>4.0</v>
       </c>
-      <c r="G44" s="47">
+      <c r="G44" s="49">
         <f t="shared" si="2"/>
         <v>2</v>
       </c>
-      <c r="H44" s="49" t="s">
-        <v>43</v>
+      <c r="H44" s="51" t="s">
+        <v>45</v>
       </c>
       <c r="I44" s="1"/>
       <c r="J44" s="1"/>
@@ -3179,22 +3199,22 @@
     </row>
     <row r="45" ht="48.75" customHeight="1">
       <c r="A45" s="1"/>
-      <c r="B45" s="53" t="s">
-        <v>76</v>
-      </c>
-      <c r="C45" s="44" t="s">
-        <v>71</v>
-      </c>
-      <c r="D45" s="48" t="s">
-        <v>77</v>
-      </c>
-      <c r="E45" s="46">
+      <c r="B45" s="55" t="s">
+        <v>78</v>
+      </c>
+      <c r="C45" s="46" t="s">
+        <v>73</v>
+      </c>
+      <c r="D45" s="50" t="s">
+        <v>79</v>
+      </c>
+      <c r="E45" s="48">
         <v>1.0</v>
       </c>
       <c r="F45" s="25">
         <v>4.0</v>
       </c>
-      <c r="G45" s="47">
+      <c r="G45" s="49">
         <f t="shared" si="2"/>
         <v>4</v>
       </c>
@@ -3220,22 +3240,22 @@
     </row>
     <row r="46" ht="46.5" customHeight="1">
       <c r="A46" s="1"/>
-      <c r="B46" s="53" t="s">
-        <v>78</v>
-      </c>
-      <c r="C46" s="44" t="s">
-        <v>71</v>
-      </c>
-      <c r="D46" s="48" t="s">
-        <v>79</v>
-      </c>
-      <c r="E46" s="46">
+      <c r="B46" s="55" t="s">
+        <v>80</v>
+      </c>
+      <c r="C46" s="46" t="s">
+        <v>73</v>
+      </c>
+      <c r="D46" s="50" t="s">
+        <v>81</v>
+      </c>
+      <c r="E46" s="48">
         <v>0.5</v>
       </c>
       <c r="F46" s="25">
         <v>3.0</v>
       </c>
-      <c r="G46" s="47">
+      <c r="G46" s="49">
         <f t="shared" si="2"/>
         <v>1.5</v>
       </c>
@@ -3261,22 +3281,22 @@
     </row>
     <row r="47" ht="37.5" customHeight="1">
       <c r="A47" s="1"/>
-      <c r="B47" s="53" t="s">
-        <v>80</v>
-      </c>
-      <c r="C47" s="44" t="s">
-        <v>81</v>
-      </c>
-      <c r="D47" s="45" t="s">
+      <c r="B47" s="55" t="s">
         <v>82</v>
       </c>
-      <c r="E47" s="46">
+      <c r="C47" s="46" t="s">
+        <v>83</v>
+      </c>
+      <c r="D47" s="47" t="s">
+        <v>84</v>
+      </c>
+      <c r="E47" s="48">
         <v>1.0</v>
       </c>
       <c r="F47" s="25">
         <v>4.0</v>
       </c>
-      <c r="G47" s="47">
+      <c r="G47" s="49">
         <f t="shared" si="2"/>
         <v>4</v>
       </c>
@@ -3302,22 +3322,22 @@
     </row>
     <row r="48" ht="43.5" customHeight="1">
       <c r="A48" s="1"/>
-      <c r="B48" s="53" t="s">
-        <v>83</v>
-      </c>
-      <c r="C48" s="44" t="s">
-        <v>84</v>
-      </c>
-      <c r="D48" s="45" t="s">
+      <c r="B48" s="55" t="s">
         <v>85</v>
       </c>
-      <c r="E48" s="46">
+      <c r="C48" s="46" t="s">
+        <v>86</v>
+      </c>
+      <c r="D48" s="47" t="s">
+        <v>87</v>
+      </c>
+      <c r="E48" s="48">
         <v>2.0</v>
       </c>
       <c r="F48" s="25">
         <v>2.0</v>
       </c>
-      <c r="G48" s="47">
+      <c r="G48" s="49">
         <f t="shared" si="2"/>
         <v>4</v>
       </c>
@@ -3343,22 +3363,22 @@
     </row>
     <row r="49" ht="71.25" customHeight="1">
       <c r="A49" s="1"/>
-      <c r="B49" s="53" t="s">
-        <v>86</v>
-      </c>
-      <c r="C49" s="44" t="s">
-        <v>87</v>
-      </c>
-      <c r="D49" s="48" t="s">
+      <c r="B49" s="55" t="s">
         <v>88</v>
       </c>
-      <c r="E49" s="46">
+      <c r="C49" s="46" t="s">
+        <v>89</v>
+      </c>
+      <c r="D49" s="50" t="s">
+        <v>90</v>
+      </c>
+      <c r="E49" s="48">
         <v>-1.0</v>
       </c>
       <c r="F49" s="25">
         <v>4.0</v>
       </c>
-      <c r="G49" s="47">
+      <c r="G49" s="49">
         <f t="shared" si="2"/>
         <v>-4</v>
       </c>
@@ -3384,22 +3404,22 @@
     </row>
     <row r="50" ht="62.25" customHeight="1">
       <c r="A50" s="1"/>
-      <c r="B50" s="53" t="s">
-        <v>89</v>
-      </c>
-      <c r="C50" s="44" t="s">
-        <v>90</v>
-      </c>
-      <c r="D50" s="48" t="s">
+      <c r="B50" s="55" t="s">
         <v>91</v>
       </c>
-      <c r="E50" s="46">
+      <c r="C50" s="46" t="s">
+        <v>92</v>
+      </c>
+      <c r="D50" s="50" t="s">
+        <v>93</v>
+      </c>
+      <c r="E50" s="48">
         <v>-1.0</v>
       </c>
       <c r="F50" s="25">
         <v>4.0</v>
       </c>
-      <c r="G50" s="47">
+      <c r="G50" s="49">
         <f t="shared" si="2"/>
         <v>-4</v>
       </c>
@@ -3426,7 +3446,7 @@
     <row r="51" ht="38.25" customHeight="1">
       <c r="A51" s="1"/>
       <c r="B51" s="28" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C51" s="6"/>
       <c r="D51" s="6"/>
@@ -3459,7 +3479,7 @@
     <row r="52" ht="27.75" customHeight="1">
       <c r="A52" s="1"/>
       <c r="B52" s="28" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C52" s="6"/>
       <c r="D52" s="6"/>
@@ -3492,11 +3512,11 @@
     <row r="53" ht="27.75" customHeight="1">
       <c r="A53" s="1"/>
       <c r="B53" s="28"/>
-      <c r="C53" s="54"/>
-      <c r="D53" s="55"/>
-      <c r="E53" s="54"/>
-      <c r="F53" s="56" t="s">
-        <v>94</v>
+      <c r="C53" s="56"/>
+      <c r="D53" s="57"/>
+      <c r="E53" s="56"/>
+      <c r="F53" s="58" t="s">
+        <v>96</v>
       </c>
       <c r="G53" s="19">
         <f>COUNTIF($F$43:$F$48,"&lt;3")+COUNTIF($F$49:$F$50,"&gt;3")</f>
@@ -3580,18 +3600,18 @@
     </row>
     <row r="56" ht="27.75" customHeight="1">
       <c r="A56" s="18" t="s">
-        <v>95</v>
-      </c>
-      <c r="B56" s="57" t="s">
-        <v>96</v>
+        <v>97</v>
+      </c>
+      <c r="B56" s="59" t="s">
+        <v>98</v>
       </c>
       <c r="C56" s="6"/>
       <c r="D56" s="6"/>
       <c r="E56" s="6"/>
       <c r="F56" s="7"/>
-      <c r="G56" s="58">
+      <c r="G56" s="60">
         <f>F21*G39*G52</f>
-        <v>31.1584</v>
+        <v>36.7224</v>
       </c>
       <c r="H56" s="1"/>
       <c r="I56" s="1"/>
@@ -3670,22 +3690,22 @@
       <c r="Z58" s="1"/>
     </row>
     <row r="59" ht="27.75" customHeight="1">
-      <c r="A59" s="59" t="s">
-        <v>97</v>
+      <c r="A59" s="61" t="s">
+        <v>99</v>
       </c>
       <c r="B59" s="20" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C59" s="20" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="D59" s="20" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="E59" s="3"/>
       <c r="F59" s="1"/>
       <c r="G59" s="20" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="H59" s="1"/>
       <c r="I59" s="1"/>
@@ -3709,20 +3729,20 @@
     </row>
     <row r="60" ht="31.5" customHeight="1">
       <c r="A60" s="1"/>
-      <c r="B60" s="60">
+      <c r="B60" s="62">
         <v>20.0</v>
       </c>
-      <c r="C60" s="60">
+      <c r="C60" s="62">
         <f>IF($G$53&gt;=5,36,IF(AND(G$53&gt;2,$G$53&lt;=4),28, IF(AND($G$53&gt;=0,$G$53&lt;=2),20,"error")))</f>
         <v>28</v>
       </c>
-      <c r="D60" s="61">
+      <c r="D60" s="63">
         <f>IF($G$53&gt;=5,$G$60*(36/20),IF(AND($G$53&gt;2,$G$53&lt;=4),$G$60*(28/20), IF(AND($G$53&gt;=0,$G$53&lt;=2),$G$60,"error")))</f>
         <v>2.8</v>
       </c>
       <c r="E60" s="3"/>
       <c r="F60" s="1"/>
-      <c r="G60" s="62">
+      <c r="G60" s="64">
         <v>2.0</v>
       </c>
       <c r="H60" s="1"/>
@@ -3747,8 +3767,8 @@
     </row>
     <row r="61" ht="27.75" customHeight="1">
       <c r="A61" s="1"/>
-      <c r="B61" s="63" t="s">
-        <v>102</v>
+      <c r="B61" s="65" t="s">
+        <v>104</v>
       </c>
       <c r="C61" s="6"/>
       <c r="D61" s="7"/>
@@ -3776,20 +3796,20 @@
       <c r="Z61" s="1"/>
     </row>
     <row r="62" ht="27.75" customHeight="1">
-      <c r="A62" s="64" t="s">
-        <v>103</v>
-      </c>
-      <c r="B62" s="60">
+      <c r="A62" s="66" t="s">
+        <v>105</v>
+      </c>
+      <c r="B62" s="62">
         <f t="shared" ref="B62:D62" si="3">$G$56*B60</f>
-        <v>623.168</v>
-      </c>
-      <c r="C62" s="60">
+        <v>734.448</v>
+      </c>
+      <c r="C62" s="62">
         <f t="shared" si="3"/>
-        <v>872.4352</v>
-      </c>
-      <c r="D62" s="60">
+        <v>1028.2272</v>
+      </c>
+      <c r="D62" s="62">
         <f t="shared" si="3"/>
-        <v>87.24352</v>
+        <v>102.82272</v>
       </c>
       <c r="E62" s="3"/>
       <c r="F62" s="1"/>
@@ -3815,20 +3835,20 @@
       <c r="Z62" s="1"/>
     </row>
     <row r="63" ht="27.75" customHeight="1">
-      <c r="A63" s="64" t="s">
-        <v>104</v>
-      </c>
-      <c r="B63" s="65">
+      <c r="A63" s="66" t="s">
+        <v>106</v>
+      </c>
+      <c r="B63" s="67">
         <f t="shared" ref="B63:C63" si="4">B62/(22*8)</f>
-        <v>3.540727273</v>
-      </c>
-      <c r="C63" s="65">
+        <v>4.173</v>
+      </c>
+      <c r="C63" s="67">
         <f t="shared" si="4"/>
-        <v>4.957018182</v>
-      </c>
-      <c r="D63" s="66">
+        <v>5.8422</v>
+      </c>
+      <c r="D63" s="68">
         <f>D62/(22*3)</f>
-        <v>1.321871515</v>
+        <v>1.55792</v>
       </c>
       <c r="E63" s="3"/>
       <c r="F63" s="1"/>
@@ -3911,15 +3931,15 @@
     </row>
     <row r="66" ht="27.75" customHeight="1">
       <c r="A66" s="18" t="s">
-        <v>105</v>
-      </c>
-      <c r="B66" s="67" t="s">
-        <v>106</v>
-      </c>
-      <c r="C66" s="68"/>
-      <c r="D66" s="55"/>
-      <c r="E66" s="54"/>
-      <c r="F66" s="69"/>
+        <v>107</v>
+      </c>
+      <c r="B66" s="69" t="s">
+        <v>108</v>
+      </c>
+      <c r="C66" s="70"/>
+      <c r="D66" s="57"/>
+      <c r="E66" s="56"/>
+      <c r="F66" s="71"/>
       <c r="G66" s="1"/>
       <c r="H66" s="1"/>
       <c r="I66" s="1"/>
@@ -3943,20 +3963,20 @@
     </row>
     <row r="67" ht="27.75" customHeight="1">
       <c r="A67" s="1"/>
-      <c r="B67" s="43" t="s">
-        <v>107</v>
+      <c r="B67" s="45" t="s">
+        <v>109</v>
       </c>
       <c r="C67" s="19" t="s">
-        <v>108</v>
-      </c>
-      <c r="D67" s="58" t="s">
-        <v>109</v>
-      </c>
-      <c r="E67" s="58" t="s">
         <v>110</v>
       </c>
-      <c r="F67" s="58" t="s">
+      <c r="D67" s="60" t="s">
         <v>111</v>
+      </c>
+      <c r="E67" s="60" t="s">
+        <v>112</v>
+      </c>
+      <c r="F67" s="60" t="s">
+        <v>113</v>
       </c>
       <c r="G67" s="1"/>
       <c r="H67" s="1"/>
@@ -3981,23 +4001,23 @@
     </row>
     <row r="68" ht="27.75" customHeight="1">
       <c r="A68" s="1"/>
-      <c r="B68" s="70" t="s">
-        <v>112</v>
-      </c>
-      <c r="C68" s="71">
+      <c r="B68" s="72" t="s">
+        <v>114</v>
+      </c>
+      <c r="C68" s="73">
         <v>0.4</v>
       </c>
-      <c r="D68" s="65">
+      <c r="D68" s="67">
         <f t="shared" ref="D68:F68" si="5">$C68/$C$68*B$63</f>
-        <v>3.540727273</v>
-      </c>
-      <c r="E68" s="65">
+        <v>4.173</v>
+      </c>
+      <c r="E68" s="67">
         <f t="shared" si="5"/>
-        <v>4.957018182</v>
-      </c>
-      <c r="F68" s="65">
+        <v>5.8422</v>
+      </c>
+      <c r="F68" s="67">
         <f t="shared" si="5"/>
-        <v>1.321871515</v>
+        <v>1.55792</v>
       </c>
       <c r="G68" s="1"/>
       <c r="H68" s="1"/>
@@ -4022,24 +4042,24 @@
     </row>
     <row r="69" ht="27.75" customHeight="1">
       <c r="A69" s="1"/>
-      <c r="B69" s="70" t="s">
-        <v>113</v>
-      </c>
-      <c r="C69" s="71">
+      <c r="B69" s="72" t="s">
+        <v>115</v>
+      </c>
+      <c r="C69" s="73">
         <f>1-C68</f>
         <v>0.6</v>
       </c>
-      <c r="D69" s="60">
+      <c r="D69" s="62">
         <f t="shared" ref="D69:F69" si="6">$C69/$C$68*B$63</f>
-        <v>5.311090909</v>
-      </c>
-      <c r="E69" s="60">
+        <v>6.2595</v>
+      </c>
+      <c r="E69" s="62">
         <f t="shared" si="6"/>
-        <v>7.435527273</v>
-      </c>
-      <c r="F69" s="60">
+        <v>8.7633</v>
+      </c>
+      <c r="F69" s="62">
         <f t="shared" si="6"/>
-        <v>1.982807273</v>
+        <v>2.33688</v>
       </c>
       <c r="G69" s="1"/>
       <c r="H69" s="1"/>
@@ -4064,22 +4084,22 @@
     </row>
     <row r="70" ht="27.75" customHeight="1">
       <c r="A70" s="1"/>
-      <c r="B70" s="72"/>
-      <c r="C70" s="71">
+      <c r="B70" s="74"/>
+      <c r="C70" s="73">
         <f>SUM(C68:C69)</f>
         <v>1</v>
       </c>
-      <c r="D70" s="65">
+      <c r="D70" s="67">
         <f t="shared" ref="D70:F70" si="7">$C70/$C$68*B$63</f>
-        <v>8.851818182</v>
-      </c>
-      <c r="E70" s="65">
+        <v>10.4325</v>
+      </c>
+      <c r="E70" s="67">
         <f t="shared" si="7"/>
-        <v>12.39254545</v>
-      </c>
-      <c r="F70" s="65">
+        <v>14.6055</v>
+      </c>
+      <c r="F70" s="67">
         <f t="shared" si="7"/>
-        <v>3.304678788</v>
+        <v>3.8948</v>
       </c>
       <c r="G70" s="1"/>
       <c r="H70" s="1"/>
@@ -4132,7 +4152,7 @@
     </row>
     <row r="72" ht="27.75" customHeight="1">
       <c r="A72" s="18" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B72" s="25">
         <v>5.0</v>
@@ -4192,16 +4212,16 @@
     </row>
     <row r="74" ht="27.75" customHeight="1">
       <c r="A74" s="18" t="s">
-        <v>115</v>
-      </c>
-      <c r="B74" s="58" t="s">
-        <v>116</v>
-      </c>
-      <c r="C74" s="58" t="s">
         <v>117</v>
       </c>
-      <c r="D74" s="58" t="s">
+      <c r="B74" s="60" t="s">
         <v>118</v>
+      </c>
+      <c r="C74" s="60" t="s">
+        <v>119</v>
+      </c>
+      <c r="D74" s="60" t="s">
+        <v>120</v>
       </c>
       <c r="E74" s="3"/>
       <c r="F74" s="1"/>
@@ -4227,22 +4247,22 @@
       <c r="Z74" s="1"/>
     </row>
     <row r="75" ht="27.75" customHeight="1">
-      <c r="A75" s="73"/>
-      <c r="B75" s="74">
+      <c r="A75" s="75"/>
+      <c r="B75" s="76">
         <f>$D$70/$B$72</f>
-        <v>1.770363636</v>
-      </c>
-      <c r="C75" s="74">
+        <v>2.0865</v>
+      </c>
+      <c r="C75" s="76">
         <f>$E$70/$B$72</f>
-        <v>2.478509091</v>
-      </c>
-      <c r="D75" s="74">
+        <v>2.9211</v>
+      </c>
+      <c r="D75" s="76">
         <f>$F$70/$B$72</f>
-        <v>0.6609357576</v>
-      </c>
-      <c r="E75" s="73"/>
-      <c r="F75" s="73"/>
-      <c r="G75" s="73"/>
+        <v>0.77896</v>
+      </c>
+      <c r="E75" s="75"/>
+      <c r="F75" s="75"/>
+      <c r="G75" s="75"/>
       <c r="H75" s="1"/>
       <c r="I75" s="1"/>
       <c r="J75" s="1"/>
@@ -4264,452 +4284,452 @@
       <c r="Z75" s="1"/>
     </row>
     <row r="76" ht="27.75" customHeight="1">
-      <c r="A76" s="73"/>
-      <c r="B76" s="73"/>
-      <c r="C76" s="73"/>
-      <c r="D76" s="73"/>
-      <c r="E76" s="75"/>
-      <c r="F76" s="73"/>
-      <c r="G76" s="73"/>
-      <c r="H76" s="73"/>
-      <c r="I76" s="73"/>
-      <c r="J76" s="73"/>
-      <c r="K76" s="73"/>
-      <c r="L76" s="73"/>
-      <c r="M76" s="73"/>
-      <c r="N76" s="73"/>
-      <c r="O76" s="73"/>
-      <c r="P76" s="73"/>
-      <c r="Q76" s="73"/>
-      <c r="R76" s="73"/>
-      <c r="S76" s="73"/>
-      <c r="T76" s="73"/>
-      <c r="U76" s="73"/>
-      <c r="V76" s="73"/>
-      <c r="W76" s="73"/>
-      <c r="X76" s="73"/>
-      <c r="Y76" s="73"/>
-      <c r="Z76" s="73"/>
+      <c r="A76" s="75"/>
+      <c r="B76" s="75"/>
+      <c r="C76" s="75"/>
+      <c r="D76" s="75"/>
+      <c r="E76" s="77"/>
+      <c r="F76" s="75"/>
+      <c r="G76" s="75"/>
+      <c r="H76" s="75"/>
+      <c r="I76" s="75"/>
+      <c r="J76" s="75"/>
+      <c r="K76" s="75"/>
+      <c r="L76" s="75"/>
+      <c r="M76" s="75"/>
+      <c r="N76" s="75"/>
+      <c r="O76" s="75"/>
+      <c r="P76" s="75"/>
+      <c r="Q76" s="75"/>
+      <c r="R76" s="75"/>
+      <c r="S76" s="75"/>
+      <c r="T76" s="75"/>
+      <c r="U76" s="75"/>
+      <c r="V76" s="75"/>
+      <c r="W76" s="75"/>
+      <c r="X76" s="75"/>
+      <c r="Y76" s="75"/>
+      <c r="Z76" s="75"/>
     </row>
     <row r="77" ht="15.75" customHeight="1">
-      <c r="A77" s="73"/>
-      <c r="B77" s="73"/>
-      <c r="C77" s="73"/>
-      <c r="D77" s="73"/>
-      <c r="E77" s="75"/>
-      <c r="F77" s="73"/>
-      <c r="G77" s="73"/>
-      <c r="H77" s="73"/>
-      <c r="I77" s="73"/>
-      <c r="J77" s="73"/>
-      <c r="K77" s="73"/>
-      <c r="L77" s="73"/>
-      <c r="M77" s="73"/>
-      <c r="N77" s="73"/>
-      <c r="O77" s="73"/>
-      <c r="P77" s="73"/>
-      <c r="Q77" s="73"/>
-      <c r="R77" s="73"/>
-      <c r="S77" s="73"/>
-      <c r="T77" s="73"/>
-      <c r="U77" s="73"/>
-      <c r="V77" s="73"/>
-      <c r="W77" s="73"/>
-      <c r="X77" s="73"/>
-      <c r="Y77" s="73"/>
-      <c r="Z77" s="73"/>
+      <c r="A77" s="75"/>
+      <c r="B77" s="75"/>
+      <c r="C77" s="75"/>
+      <c r="D77" s="75"/>
+      <c r="E77" s="77"/>
+      <c r="F77" s="75"/>
+      <c r="G77" s="75"/>
+      <c r="H77" s="75"/>
+      <c r="I77" s="75"/>
+      <c r="J77" s="75"/>
+      <c r="K77" s="75"/>
+      <c r="L77" s="75"/>
+      <c r="M77" s="75"/>
+      <c r="N77" s="75"/>
+      <c r="O77" s="75"/>
+      <c r="P77" s="75"/>
+      <c r="Q77" s="75"/>
+      <c r="R77" s="75"/>
+      <c r="S77" s="75"/>
+      <c r="T77" s="75"/>
+      <c r="U77" s="75"/>
+      <c r="V77" s="75"/>
+      <c r="W77" s="75"/>
+      <c r="X77" s="75"/>
+      <c r="Y77" s="75"/>
+      <c r="Z77" s="75"/>
     </row>
     <row r="78" ht="15.75" customHeight="1">
-      <c r="A78" s="73"/>
-      <c r="B78" s="73"/>
-      <c r="C78" s="73"/>
-      <c r="D78" s="73"/>
-      <c r="E78" s="75"/>
-      <c r="F78" s="73"/>
-      <c r="G78" s="73"/>
-      <c r="H78" s="73"/>
-      <c r="I78" s="73"/>
-      <c r="J78" s="73"/>
-      <c r="K78" s="73"/>
-      <c r="L78" s="73"/>
-      <c r="M78" s="73"/>
-      <c r="N78" s="73"/>
-      <c r="O78" s="73"/>
-      <c r="P78" s="73"/>
-      <c r="Q78" s="73"/>
-      <c r="R78" s="73"/>
-      <c r="S78" s="73"/>
-      <c r="T78" s="73"/>
-      <c r="U78" s="73"/>
-      <c r="V78" s="73"/>
-      <c r="W78" s="73"/>
-      <c r="X78" s="73"/>
-      <c r="Y78" s="73"/>
-      <c r="Z78" s="73"/>
+      <c r="A78" s="75"/>
+      <c r="B78" s="75"/>
+      <c r="C78" s="75"/>
+      <c r="D78" s="75"/>
+      <c r="E78" s="77"/>
+      <c r="F78" s="75"/>
+      <c r="G78" s="75"/>
+      <c r="H78" s="75"/>
+      <c r="I78" s="75"/>
+      <c r="J78" s="75"/>
+      <c r="K78" s="75"/>
+      <c r="L78" s="75"/>
+      <c r="M78" s="75"/>
+      <c r="N78" s="75"/>
+      <c r="O78" s="75"/>
+      <c r="P78" s="75"/>
+      <c r="Q78" s="75"/>
+      <c r="R78" s="75"/>
+      <c r="S78" s="75"/>
+      <c r="T78" s="75"/>
+      <c r="U78" s="75"/>
+      <c r="V78" s="75"/>
+      <c r="W78" s="75"/>
+      <c r="X78" s="75"/>
+      <c r="Y78" s="75"/>
+      <c r="Z78" s="75"/>
     </row>
     <row r="79" ht="15.75" customHeight="1">
-      <c r="A79" s="73"/>
-      <c r="B79" s="73"/>
-      <c r="C79" s="73"/>
-      <c r="D79" s="73"/>
-      <c r="E79" s="75"/>
-      <c r="F79" s="73"/>
-      <c r="G79" s="73"/>
-      <c r="H79" s="73"/>
-      <c r="I79" s="73"/>
-      <c r="J79" s="73"/>
-      <c r="K79" s="73"/>
-      <c r="L79" s="73"/>
-      <c r="M79" s="73"/>
-      <c r="N79" s="73"/>
-      <c r="O79" s="73"/>
-      <c r="P79" s="73"/>
-      <c r="Q79" s="73"/>
-      <c r="R79" s="73"/>
-      <c r="S79" s="73"/>
-      <c r="T79" s="73"/>
-      <c r="U79" s="73"/>
-      <c r="V79" s="73"/>
-      <c r="W79" s="73"/>
-      <c r="X79" s="73"/>
-      <c r="Y79" s="73"/>
-      <c r="Z79" s="73"/>
+      <c r="A79" s="75"/>
+      <c r="B79" s="75"/>
+      <c r="C79" s="75"/>
+      <c r="D79" s="75"/>
+      <c r="E79" s="77"/>
+      <c r="F79" s="75"/>
+      <c r="G79" s="75"/>
+      <c r="H79" s="75"/>
+      <c r="I79" s="75"/>
+      <c r="J79" s="75"/>
+      <c r="K79" s="75"/>
+      <c r="L79" s="75"/>
+      <c r="M79" s="75"/>
+      <c r="N79" s="75"/>
+      <c r="O79" s="75"/>
+      <c r="P79" s="75"/>
+      <c r="Q79" s="75"/>
+      <c r="R79" s="75"/>
+      <c r="S79" s="75"/>
+      <c r="T79" s="75"/>
+      <c r="U79" s="75"/>
+      <c r="V79" s="75"/>
+      <c r="W79" s="75"/>
+      <c r="X79" s="75"/>
+      <c r="Y79" s="75"/>
+      <c r="Z79" s="75"/>
     </row>
     <row r="80" ht="15.75" customHeight="1">
-      <c r="A80" s="73"/>
-      <c r="B80" s="73"/>
-      <c r="C80" s="73"/>
-      <c r="D80" s="73"/>
-      <c r="E80" s="75"/>
-      <c r="F80" s="73"/>
-      <c r="G80" s="73"/>
-      <c r="H80" s="73"/>
-      <c r="I80" s="73"/>
-      <c r="J80" s="73"/>
-      <c r="K80" s="73"/>
-      <c r="L80" s="73"/>
-      <c r="M80" s="73"/>
-      <c r="N80" s="73"/>
-      <c r="O80" s="73"/>
-      <c r="P80" s="73"/>
-      <c r="Q80" s="73"/>
-      <c r="R80" s="73"/>
-      <c r="S80" s="73"/>
-      <c r="T80" s="73"/>
-      <c r="U80" s="73"/>
-      <c r="V80" s="73"/>
-      <c r="W80" s="73"/>
-      <c r="X80" s="73"/>
-      <c r="Y80" s="73"/>
-      <c r="Z80" s="73"/>
+      <c r="A80" s="75"/>
+      <c r="B80" s="75"/>
+      <c r="C80" s="75"/>
+      <c r="D80" s="75"/>
+      <c r="E80" s="77"/>
+      <c r="F80" s="75"/>
+      <c r="G80" s="75"/>
+      <c r="H80" s="75"/>
+      <c r="I80" s="75"/>
+      <c r="J80" s="75"/>
+      <c r="K80" s="75"/>
+      <c r="L80" s="75"/>
+      <c r="M80" s="75"/>
+      <c r="N80" s="75"/>
+      <c r="O80" s="75"/>
+      <c r="P80" s="75"/>
+      <c r="Q80" s="75"/>
+      <c r="R80" s="75"/>
+      <c r="S80" s="75"/>
+      <c r="T80" s="75"/>
+      <c r="U80" s="75"/>
+      <c r="V80" s="75"/>
+      <c r="W80" s="75"/>
+      <c r="X80" s="75"/>
+      <c r="Y80" s="75"/>
+      <c r="Z80" s="75"/>
     </row>
     <row r="81" ht="15.75" customHeight="1">
-      <c r="A81" s="73"/>
-      <c r="B81" s="73"/>
-      <c r="C81" s="73"/>
-      <c r="D81" s="73"/>
-      <c r="E81" s="75"/>
-      <c r="F81" s="73"/>
-      <c r="G81" s="73"/>
-      <c r="H81" s="73"/>
-      <c r="I81" s="73"/>
-      <c r="J81" s="73"/>
-      <c r="K81" s="73"/>
-      <c r="L81" s="73"/>
-      <c r="M81" s="73"/>
-      <c r="N81" s="73"/>
-      <c r="O81" s="73"/>
-      <c r="P81" s="73"/>
-      <c r="Q81" s="73"/>
-      <c r="R81" s="73"/>
-      <c r="S81" s="73"/>
-      <c r="T81" s="73"/>
-      <c r="U81" s="73"/>
-      <c r="V81" s="73"/>
-      <c r="W81" s="73"/>
-      <c r="X81" s="73"/>
-      <c r="Y81" s="73"/>
-      <c r="Z81" s="73"/>
+      <c r="A81" s="75"/>
+      <c r="B81" s="75"/>
+      <c r="C81" s="75"/>
+      <c r="D81" s="75"/>
+      <c r="E81" s="77"/>
+      <c r="F81" s="75"/>
+      <c r="G81" s="75"/>
+      <c r="H81" s="75"/>
+      <c r="I81" s="75"/>
+      <c r="J81" s="75"/>
+      <c r="K81" s="75"/>
+      <c r="L81" s="75"/>
+      <c r="M81" s="75"/>
+      <c r="N81" s="75"/>
+      <c r="O81" s="75"/>
+      <c r="P81" s="75"/>
+      <c r="Q81" s="75"/>
+      <c r="R81" s="75"/>
+      <c r="S81" s="75"/>
+      <c r="T81" s="75"/>
+      <c r="U81" s="75"/>
+      <c r="V81" s="75"/>
+      <c r="W81" s="75"/>
+      <c r="X81" s="75"/>
+      <c r="Y81" s="75"/>
+      <c r="Z81" s="75"/>
     </row>
     <row r="82" ht="15.75" customHeight="1">
-      <c r="A82" s="73"/>
-      <c r="B82" s="73"/>
-      <c r="C82" s="73"/>
-      <c r="D82" s="73"/>
-      <c r="E82" s="75"/>
-      <c r="F82" s="73"/>
-      <c r="G82" s="73"/>
-      <c r="H82" s="73"/>
-      <c r="I82" s="73"/>
-      <c r="J82" s="73"/>
-      <c r="K82" s="73"/>
-      <c r="L82" s="73"/>
-      <c r="M82" s="73"/>
-      <c r="N82" s="73"/>
-      <c r="O82" s="73"/>
-      <c r="P82" s="73"/>
-      <c r="Q82" s="73"/>
-      <c r="R82" s="73"/>
-      <c r="S82" s="73"/>
-      <c r="T82" s="73"/>
-      <c r="U82" s="73"/>
-      <c r="V82" s="73"/>
-      <c r="W82" s="73"/>
-      <c r="X82" s="73"/>
-      <c r="Y82" s="73"/>
-      <c r="Z82" s="73"/>
+      <c r="A82" s="75"/>
+      <c r="B82" s="75"/>
+      <c r="C82" s="75"/>
+      <c r="D82" s="75"/>
+      <c r="E82" s="77"/>
+      <c r="F82" s="75"/>
+      <c r="G82" s="75"/>
+      <c r="H82" s="75"/>
+      <c r="I82" s="75"/>
+      <c r="J82" s="75"/>
+      <c r="K82" s="75"/>
+      <c r="L82" s="75"/>
+      <c r="M82" s="75"/>
+      <c r="N82" s="75"/>
+      <c r="O82" s="75"/>
+      <c r="P82" s="75"/>
+      <c r="Q82" s="75"/>
+      <c r="R82" s="75"/>
+      <c r="S82" s="75"/>
+      <c r="T82" s="75"/>
+      <c r="U82" s="75"/>
+      <c r="V82" s="75"/>
+      <c r="W82" s="75"/>
+      <c r="X82" s="75"/>
+      <c r="Y82" s="75"/>
+      <c r="Z82" s="75"/>
     </row>
     <row r="83" ht="15.75" customHeight="1">
-      <c r="A83" s="73"/>
-      <c r="B83" s="73"/>
-      <c r="C83" s="73"/>
-      <c r="D83" s="73"/>
-      <c r="E83" s="75"/>
-      <c r="F83" s="73"/>
-      <c r="G83" s="73"/>
-      <c r="H83" s="73"/>
-      <c r="I83" s="73"/>
-      <c r="J83" s="73"/>
-      <c r="K83" s="73"/>
-      <c r="L83" s="73"/>
-      <c r="M83" s="73"/>
-      <c r="N83" s="73"/>
-      <c r="O83" s="73"/>
-      <c r="P83" s="73"/>
-      <c r="Q83" s="73"/>
-      <c r="R83" s="73"/>
-      <c r="S83" s="73"/>
-      <c r="T83" s="73"/>
-      <c r="U83" s="73"/>
-      <c r="V83" s="73"/>
-      <c r="W83" s="73"/>
-      <c r="X83" s="73"/>
-      <c r="Y83" s="73"/>
-      <c r="Z83" s="73"/>
+      <c r="A83" s="75"/>
+      <c r="B83" s="75"/>
+      <c r="C83" s="75"/>
+      <c r="D83" s="75"/>
+      <c r="E83" s="77"/>
+      <c r="F83" s="75"/>
+      <c r="G83" s="75"/>
+      <c r="H83" s="75"/>
+      <c r="I83" s="75"/>
+      <c r="J83" s="75"/>
+      <c r="K83" s="75"/>
+      <c r="L83" s="75"/>
+      <c r="M83" s="75"/>
+      <c r="N83" s="75"/>
+      <c r="O83" s="75"/>
+      <c r="P83" s="75"/>
+      <c r="Q83" s="75"/>
+      <c r="R83" s="75"/>
+      <c r="S83" s="75"/>
+      <c r="T83" s="75"/>
+      <c r="U83" s="75"/>
+      <c r="V83" s="75"/>
+      <c r="W83" s="75"/>
+      <c r="X83" s="75"/>
+      <c r="Y83" s="75"/>
+      <c r="Z83" s="75"/>
     </row>
     <row r="84" ht="15.75" customHeight="1">
-      <c r="A84" s="73"/>
-      <c r="B84" s="73"/>
-      <c r="C84" s="73"/>
-      <c r="D84" s="73"/>
-      <c r="E84" s="75"/>
-      <c r="F84" s="73"/>
-      <c r="G84" s="73"/>
-      <c r="H84" s="73"/>
-      <c r="I84" s="73"/>
-      <c r="J84" s="73"/>
-      <c r="K84" s="73"/>
-      <c r="L84" s="73"/>
-      <c r="M84" s="73"/>
-      <c r="N84" s="73"/>
-      <c r="O84" s="73"/>
-      <c r="P84" s="73"/>
-      <c r="Q84" s="73"/>
-      <c r="R84" s="73"/>
-      <c r="S84" s="73"/>
-      <c r="T84" s="73"/>
-      <c r="U84" s="73"/>
-      <c r="V84" s="73"/>
-      <c r="W84" s="73"/>
-      <c r="X84" s="73"/>
-      <c r="Y84" s="73"/>
-      <c r="Z84" s="73"/>
+      <c r="A84" s="75"/>
+      <c r="B84" s="75"/>
+      <c r="C84" s="75"/>
+      <c r="D84" s="75"/>
+      <c r="E84" s="77"/>
+      <c r="F84" s="75"/>
+      <c r="G84" s="75"/>
+      <c r="H84" s="75"/>
+      <c r="I84" s="75"/>
+      <c r="J84" s="75"/>
+      <c r="K84" s="75"/>
+      <c r="L84" s="75"/>
+      <c r="M84" s="75"/>
+      <c r="N84" s="75"/>
+      <c r="O84" s="75"/>
+      <c r="P84" s="75"/>
+      <c r="Q84" s="75"/>
+      <c r="R84" s="75"/>
+      <c r="S84" s="75"/>
+      <c r="T84" s="75"/>
+      <c r="U84" s="75"/>
+      <c r="V84" s="75"/>
+      <c r="W84" s="75"/>
+      <c r="X84" s="75"/>
+      <c r="Y84" s="75"/>
+      <c r="Z84" s="75"/>
     </row>
     <row r="85" ht="15.75" customHeight="1">
-      <c r="A85" s="73"/>
-      <c r="B85" s="73"/>
-      <c r="C85" s="73"/>
-      <c r="D85" s="73"/>
-      <c r="E85" s="75"/>
-      <c r="F85" s="73"/>
-      <c r="G85" s="73"/>
-      <c r="H85" s="73"/>
-      <c r="I85" s="73"/>
-      <c r="J85" s="73"/>
-      <c r="K85" s="73"/>
-      <c r="L85" s="73"/>
-      <c r="M85" s="73"/>
-      <c r="N85" s="73"/>
-      <c r="O85" s="73"/>
-      <c r="P85" s="73"/>
-      <c r="Q85" s="73"/>
-      <c r="R85" s="73"/>
-      <c r="S85" s="73"/>
-      <c r="T85" s="73"/>
-      <c r="U85" s="73"/>
-      <c r="V85" s="73"/>
-      <c r="W85" s="73"/>
-      <c r="X85" s="73"/>
-      <c r="Y85" s="73"/>
-      <c r="Z85" s="73"/>
+      <c r="A85" s="75"/>
+      <c r="B85" s="75"/>
+      <c r="C85" s="75"/>
+      <c r="D85" s="75"/>
+      <c r="E85" s="77"/>
+      <c r="F85" s="75"/>
+      <c r="G85" s="75"/>
+      <c r="H85" s="75"/>
+      <c r="I85" s="75"/>
+      <c r="J85" s="75"/>
+      <c r="K85" s="75"/>
+      <c r="L85" s="75"/>
+      <c r="M85" s="75"/>
+      <c r="N85" s="75"/>
+      <c r="O85" s="75"/>
+      <c r="P85" s="75"/>
+      <c r="Q85" s="75"/>
+      <c r="R85" s="75"/>
+      <c r="S85" s="75"/>
+      <c r="T85" s="75"/>
+      <c r="U85" s="75"/>
+      <c r="V85" s="75"/>
+      <c r="W85" s="75"/>
+      <c r="X85" s="75"/>
+      <c r="Y85" s="75"/>
+      <c r="Z85" s="75"/>
     </row>
     <row r="86" ht="15.75" customHeight="1">
-      <c r="A86" s="73"/>
-      <c r="B86" s="73"/>
-      <c r="C86" s="73"/>
-      <c r="D86" s="73"/>
-      <c r="E86" s="75"/>
-      <c r="F86" s="73"/>
-      <c r="G86" s="73"/>
-      <c r="H86" s="73"/>
-      <c r="I86" s="73"/>
-      <c r="J86" s="73"/>
-      <c r="K86" s="73"/>
-      <c r="L86" s="73"/>
-      <c r="M86" s="73"/>
-      <c r="N86" s="73"/>
-      <c r="O86" s="73"/>
-      <c r="P86" s="73"/>
-      <c r="Q86" s="73"/>
-      <c r="R86" s="73"/>
-      <c r="S86" s="73"/>
-      <c r="T86" s="73"/>
-      <c r="U86" s="73"/>
-      <c r="V86" s="73"/>
-      <c r="W86" s="73"/>
-      <c r="X86" s="73"/>
-      <c r="Y86" s="73"/>
-      <c r="Z86" s="73"/>
+      <c r="A86" s="75"/>
+      <c r="B86" s="75"/>
+      <c r="C86" s="75"/>
+      <c r="D86" s="75"/>
+      <c r="E86" s="77"/>
+      <c r="F86" s="75"/>
+      <c r="G86" s="75"/>
+      <c r="H86" s="75"/>
+      <c r="I86" s="75"/>
+      <c r="J86" s="75"/>
+      <c r="K86" s="75"/>
+      <c r="L86" s="75"/>
+      <c r="M86" s="75"/>
+      <c r="N86" s="75"/>
+      <c r="O86" s="75"/>
+      <c r="P86" s="75"/>
+      <c r="Q86" s="75"/>
+      <c r="R86" s="75"/>
+      <c r="S86" s="75"/>
+      <c r="T86" s="75"/>
+      <c r="U86" s="75"/>
+      <c r="V86" s="75"/>
+      <c r="W86" s="75"/>
+      <c r="X86" s="75"/>
+      <c r="Y86" s="75"/>
+      <c r="Z86" s="75"/>
     </row>
     <row r="87" ht="15.75" customHeight="1">
-      <c r="A87" s="73"/>
-      <c r="B87" s="73"/>
-      <c r="C87" s="73"/>
-      <c r="D87" s="73"/>
-      <c r="E87" s="75"/>
-      <c r="F87" s="73"/>
-      <c r="G87" s="73"/>
-      <c r="H87" s="73"/>
-      <c r="I87" s="73"/>
-      <c r="J87" s="73"/>
-      <c r="K87" s="73"/>
-      <c r="L87" s="73"/>
-      <c r="M87" s="73"/>
-      <c r="N87" s="73"/>
-      <c r="O87" s="73"/>
-      <c r="P87" s="73"/>
-      <c r="Q87" s="73"/>
-      <c r="R87" s="73"/>
-      <c r="S87" s="73"/>
-      <c r="T87" s="73"/>
-      <c r="U87" s="73"/>
-      <c r="V87" s="73"/>
-      <c r="W87" s="73"/>
-      <c r="X87" s="73"/>
-      <c r="Y87" s="73"/>
-      <c r="Z87" s="73"/>
+      <c r="A87" s="75"/>
+      <c r="B87" s="75"/>
+      <c r="C87" s="75"/>
+      <c r="D87" s="75"/>
+      <c r="E87" s="77"/>
+      <c r="F87" s="75"/>
+      <c r="G87" s="75"/>
+      <c r="H87" s="75"/>
+      <c r="I87" s="75"/>
+      <c r="J87" s="75"/>
+      <c r="K87" s="75"/>
+      <c r="L87" s="75"/>
+      <c r="M87" s="75"/>
+      <c r="N87" s="75"/>
+      <c r="O87" s="75"/>
+      <c r="P87" s="75"/>
+      <c r="Q87" s="75"/>
+      <c r="R87" s="75"/>
+      <c r="S87" s="75"/>
+      <c r="T87" s="75"/>
+      <c r="U87" s="75"/>
+      <c r="V87" s="75"/>
+      <c r="W87" s="75"/>
+      <c r="X87" s="75"/>
+      <c r="Y87" s="75"/>
+      <c r="Z87" s="75"/>
     </row>
     <row r="88" ht="15.75" customHeight="1">
-      <c r="A88" s="73"/>
-      <c r="B88" s="73"/>
-      <c r="C88" s="73"/>
-      <c r="D88" s="73"/>
-      <c r="E88" s="75"/>
-      <c r="F88" s="73"/>
-      <c r="G88" s="73"/>
-      <c r="H88" s="73"/>
-      <c r="I88" s="73"/>
-      <c r="J88" s="73"/>
-      <c r="K88" s="73"/>
-      <c r="L88" s="73"/>
-      <c r="M88" s="73"/>
-      <c r="N88" s="73"/>
-      <c r="O88" s="73"/>
-      <c r="P88" s="73"/>
-      <c r="Q88" s="73"/>
-      <c r="R88" s="73"/>
-      <c r="S88" s="73"/>
-      <c r="T88" s="73"/>
-      <c r="U88" s="73"/>
-      <c r="V88" s="73"/>
-      <c r="W88" s="73"/>
-      <c r="X88" s="73"/>
-      <c r="Y88" s="73"/>
-      <c r="Z88" s="73"/>
+      <c r="A88" s="75"/>
+      <c r="B88" s="75"/>
+      <c r="C88" s="75"/>
+      <c r="D88" s="75"/>
+      <c r="E88" s="77"/>
+      <c r="F88" s="75"/>
+      <c r="G88" s="75"/>
+      <c r="H88" s="75"/>
+      <c r="I88" s="75"/>
+      <c r="J88" s="75"/>
+      <c r="K88" s="75"/>
+      <c r="L88" s="75"/>
+      <c r="M88" s="75"/>
+      <c r="N88" s="75"/>
+      <c r="O88" s="75"/>
+      <c r="P88" s="75"/>
+      <c r="Q88" s="75"/>
+      <c r="R88" s="75"/>
+      <c r="S88" s="75"/>
+      <c r="T88" s="75"/>
+      <c r="U88" s="75"/>
+      <c r="V88" s="75"/>
+      <c r="W88" s="75"/>
+      <c r="X88" s="75"/>
+      <c r="Y88" s="75"/>
+      <c r="Z88" s="75"/>
     </row>
     <row r="89" ht="15.75" customHeight="1">
-      <c r="A89" s="73"/>
-      <c r="B89" s="73"/>
-      <c r="C89" s="73"/>
-      <c r="D89" s="73"/>
-      <c r="E89" s="75"/>
-      <c r="F89" s="73"/>
-      <c r="G89" s="73"/>
-      <c r="H89" s="73"/>
-      <c r="I89" s="73"/>
-      <c r="J89" s="73"/>
-      <c r="K89" s="73"/>
-      <c r="L89" s="73"/>
-      <c r="M89" s="73"/>
-      <c r="N89" s="73"/>
-      <c r="O89" s="73"/>
-      <c r="P89" s="73"/>
-      <c r="Q89" s="73"/>
-      <c r="R89" s="73"/>
-      <c r="S89" s="73"/>
-      <c r="T89" s="73"/>
-      <c r="U89" s="73"/>
-      <c r="V89" s="73"/>
-      <c r="W89" s="73"/>
-      <c r="X89" s="73"/>
-      <c r="Y89" s="73"/>
-      <c r="Z89" s="73"/>
+      <c r="A89" s="75"/>
+      <c r="B89" s="75"/>
+      <c r="C89" s="75"/>
+      <c r="D89" s="75"/>
+      <c r="E89" s="77"/>
+      <c r="F89" s="75"/>
+      <c r="G89" s="75"/>
+      <c r="H89" s="75"/>
+      <c r="I89" s="75"/>
+      <c r="J89" s="75"/>
+      <c r="K89" s="75"/>
+      <c r="L89" s="75"/>
+      <c r="M89" s="75"/>
+      <c r="N89" s="75"/>
+      <c r="O89" s="75"/>
+      <c r="P89" s="75"/>
+      <c r="Q89" s="75"/>
+      <c r="R89" s="75"/>
+      <c r="S89" s="75"/>
+      <c r="T89" s="75"/>
+      <c r="U89" s="75"/>
+      <c r="V89" s="75"/>
+      <c r="W89" s="75"/>
+      <c r="X89" s="75"/>
+      <c r="Y89" s="75"/>
+      <c r="Z89" s="75"/>
     </row>
     <row r="90" ht="15.75" customHeight="1">
-      <c r="A90" s="73"/>
-      <c r="B90" s="73"/>
-      <c r="C90" s="73"/>
-      <c r="D90" s="73"/>
-      <c r="E90" s="75"/>
-      <c r="F90" s="73"/>
-      <c r="G90" s="73"/>
-      <c r="H90" s="73"/>
-      <c r="I90" s="73"/>
-      <c r="J90" s="73"/>
-      <c r="K90" s="73"/>
-      <c r="L90" s="73"/>
-      <c r="M90" s="73"/>
-      <c r="N90" s="73"/>
-      <c r="O90" s="73"/>
-      <c r="P90" s="73"/>
-      <c r="Q90" s="73"/>
-      <c r="R90" s="73"/>
-      <c r="S90" s="73"/>
-      <c r="T90" s="73"/>
-      <c r="U90" s="73"/>
-      <c r="V90" s="73"/>
-      <c r="W90" s="73"/>
-      <c r="X90" s="73"/>
-      <c r="Y90" s="73"/>
-      <c r="Z90" s="73"/>
+      <c r="A90" s="75"/>
+      <c r="B90" s="75"/>
+      <c r="C90" s="75"/>
+      <c r="D90" s="75"/>
+      <c r="E90" s="77"/>
+      <c r="F90" s="75"/>
+      <c r="G90" s="75"/>
+      <c r="H90" s="75"/>
+      <c r="I90" s="75"/>
+      <c r="J90" s="75"/>
+      <c r="K90" s="75"/>
+      <c r="L90" s="75"/>
+      <c r="M90" s="75"/>
+      <c r="N90" s="75"/>
+      <c r="O90" s="75"/>
+      <c r="P90" s="75"/>
+      <c r="Q90" s="75"/>
+      <c r="R90" s="75"/>
+      <c r="S90" s="75"/>
+      <c r="T90" s="75"/>
+      <c r="U90" s="75"/>
+      <c r="V90" s="75"/>
+      <c r="W90" s="75"/>
+      <c r="X90" s="75"/>
+      <c r="Y90" s="75"/>
+      <c r="Z90" s="75"/>
     </row>
     <row r="91" ht="15.75" customHeight="1">
-      <c r="A91" s="73"/>
-      <c r="B91" s="73"/>
-      <c r="C91" s="73"/>
-      <c r="D91" s="73"/>
-      <c r="E91" s="75"/>
-      <c r="F91" s="73"/>
-      <c r="G91" s="73"/>
-      <c r="H91" s="73"/>
-      <c r="I91" s="73"/>
-      <c r="J91" s="73"/>
-      <c r="K91" s="73"/>
-      <c r="L91" s="73"/>
-      <c r="M91" s="73"/>
-      <c r="N91" s="73"/>
-      <c r="O91" s="73"/>
-      <c r="P91" s="73"/>
-      <c r="Q91" s="73"/>
-      <c r="R91" s="73"/>
-      <c r="S91" s="73"/>
-      <c r="T91" s="73"/>
-      <c r="U91" s="73"/>
-      <c r="V91" s="73"/>
-      <c r="W91" s="73"/>
-      <c r="X91" s="73"/>
-      <c r="Y91" s="73"/>
-      <c r="Z91" s="73"/>
+      <c r="A91" s="75"/>
+      <c r="B91" s="75"/>
+      <c r="C91" s="75"/>
+      <c r="D91" s="75"/>
+      <c r="E91" s="77"/>
+      <c r="F91" s="75"/>
+      <c r="G91" s="75"/>
+      <c r="H91" s="75"/>
+      <c r="I91" s="75"/>
+      <c r="J91" s="75"/>
+      <c r="K91" s="75"/>
+      <c r="L91" s="75"/>
+      <c r="M91" s="75"/>
+      <c r="N91" s="75"/>
+      <c r="O91" s="75"/>
+      <c r="P91" s="75"/>
+      <c r="Q91" s="75"/>
+      <c r="R91" s="75"/>
+      <c r="S91" s="75"/>
+      <c r="T91" s="75"/>
+      <c r="U91" s="75"/>
+      <c r="V91" s="75"/>
+      <c r="W91" s="75"/>
+      <c r="X91" s="75"/>
+      <c r="Y91" s="75"/>
+      <c r="Z91" s="75"/>
     </row>
     <row r="92" ht="15.75" customHeight="1">
       <c r="A92" s="1"/>
@@ -4719,25 +4739,25 @@
       <c r="E92" s="3"/>
       <c r="F92" s="1"/>
       <c r="G92" s="1"/>
-      <c r="H92" s="73"/>
-      <c r="I92" s="73"/>
-      <c r="J92" s="73"/>
-      <c r="K92" s="73"/>
-      <c r="L92" s="73"/>
-      <c r="M92" s="73"/>
-      <c r="N92" s="73"/>
-      <c r="O92" s="73"/>
-      <c r="P92" s="73"/>
-      <c r="Q92" s="73"/>
-      <c r="R92" s="73"/>
-      <c r="S92" s="73"/>
-      <c r="T92" s="73"/>
-      <c r="U92" s="73"/>
-      <c r="V92" s="73"/>
-      <c r="W92" s="73"/>
-      <c r="X92" s="73"/>
-      <c r="Y92" s="73"/>
-      <c r="Z92" s="73"/>
+      <c r="H92" s="75"/>
+      <c r="I92" s="75"/>
+      <c r="J92" s="75"/>
+      <c r="K92" s="75"/>
+      <c r="L92" s="75"/>
+      <c r="M92" s="75"/>
+      <c r="N92" s="75"/>
+      <c r="O92" s="75"/>
+      <c r="P92" s="75"/>
+      <c r="Q92" s="75"/>
+      <c r="R92" s="75"/>
+      <c r="S92" s="75"/>
+      <c r="T92" s="75"/>
+      <c r="U92" s="75"/>
+      <c r="V92" s="75"/>
+      <c r="W92" s="75"/>
+      <c r="X92" s="75"/>
+      <c r="Y92" s="75"/>
+      <c r="Z92" s="75"/>
     </row>
     <row r="93" ht="15.75" customHeight="1">
       <c r="A93" s="1"/>
